--- a/employees_CA.xlsx
+++ b/employees_CA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="161">
   <si>
     <t>Legal Name</t>
   </si>
@@ -49,12 +49,18 @@
     <t>LinkW Logistics USA Inc</t>
   </si>
   <si>
+    <t>LinkW TechChain Logistics Inc</t>
+  </si>
+  <si>
     <t>Semi-Monthly</t>
   </si>
   <si>
     <t>Kun</t>
   </si>
   <si>
+    <t>David</t>
+  </si>
+  <si>
     <t>Hong</t>
   </si>
   <si>
@@ -64,6 +70,9 @@
     <t>Xuewen</t>
   </si>
   <si>
+    <t>Ye</t>
+  </si>
+  <si>
     <t>Zhenjun</t>
   </si>
   <si>
@@ -118,6 +127,9 @@
     <t>Ting</t>
   </si>
   <si>
+    <t>Jiu</t>
+  </si>
+  <si>
     <t>KunIengCheong</t>
   </si>
   <si>
@@ -130,6 +142,9 @@
     <t>Jie</t>
   </si>
   <si>
+    <t>Yonghua</t>
+  </si>
+  <si>
     <t>Zhihong</t>
   </si>
   <si>
@@ -145,6 +160,9 @@
     <t>Jing</t>
   </si>
   <si>
+    <t>Xiaoyang</t>
+  </si>
+  <si>
     <t>Xin</t>
   </si>
   <si>
@@ -178,9 +196,15 @@
     <t>Jaime</t>
   </si>
   <si>
+    <t>Lanlan</t>
+  </si>
+  <si>
     <t>Yinghui</t>
   </si>
   <si>
+    <t>Zhaoyi</t>
+  </si>
+  <si>
     <t>Wingking</t>
   </si>
   <si>
@@ -196,18 +220,30 @@
     <t>Jiayu</t>
   </si>
   <si>
+    <t>Ying</t>
+  </si>
+  <si>
     <t>Weidong</t>
   </si>
   <si>
+    <t>Lexi</t>
+  </si>
+  <si>
     <t>Johnson</t>
   </si>
   <si>
     <t>Libang</t>
   </si>
   <si>
+    <t>Yujian</t>
+  </si>
+  <si>
     <t>Jiran</t>
   </si>
   <si>
+    <t>Xiangju</t>
+  </si>
+  <si>
     <t>Ya-Han</t>
   </si>
   <si>
@@ -232,9 +268,15 @@
     <t>Yiyu</t>
   </si>
   <si>
+    <t>Yue</t>
+  </si>
+  <si>
     <t>Yuran</t>
   </si>
   <si>
+    <t>Huan</t>
+  </si>
+  <si>
     <t>Qianyang</t>
   </si>
   <si>
@@ -370,18 +412,21 @@
     <t>Wei</t>
   </si>
   <si>
+    <t>Winstone</t>
+  </si>
+  <si>
     <t>Wu</t>
   </si>
   <si>
     <t>Xia</t>
   </si>
   <si>
+    <t>Xiong</t>
+  </si>
+  <si>
     <t>Xu</t>
   </si>
   <si>
-    <t>Yan</t>
-  </si>
-  <si>
     <t>Yang</t>
   </si>
   <si>
@@ -422,6 +467,9 @@
   </si>
   <si>
     <t>Executive - Executive</t>
+  </si>
+  <si>
+    <t>Drop-Shipp - Drop-Shipping</t>
   </si>
   <si>
     <t xml:space="preserve">Unloading - Unloading </t>
@@ -784,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -824,63 +872,63 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>195</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="F2" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G2" s="1">
         <v>45916</v>
       </c>
       <c r="H2" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="J2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>224</v>
+        <v>1012</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F3" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G3" s="1">
-        <v>46168</v>
+        <v>44929</v>
       </c>
       <c r="H3" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I3" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J3" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -888,31 +936,31 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>18</v>
+        <v>224</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G4" s="1">
-        <v>43405</v>
+        <v>46168</v>
       </c>
       <c r="H4" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I4" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J4" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -920,31 +968,31 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>222</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F5" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G5" s="1">
-        <v>46162</v>
+        <v>43405</v>
       </c>
       <c r="H5" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I5" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="J5" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -952,63 +1000,63 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F6" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G6" s="1">
-        <v>45909</v>
+        <v>46162</v>
       </c>
       <c r="H6" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I6" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J6" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>129</v>
+        <v>1040</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="F7" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G7" s="1">
-        <v>45471</v>
+        <v>45684</v>
       </c>
       <c r="H7" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I7" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J7" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1016,31 +1064,31 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F8" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G8" s="1">
-        <v>45701</v>
+        <v>45909</v>
       </c>
       <c r="H8" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I8" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J8" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1048,31 +1096,31 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9">
+        <v>129</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G9" s="1">
+        <v>45471</v>
+      </c>
+      <c r="H9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I9" t="s">
+        <v>148</v>
+      </c>
+      <c r="J9" t="s">
         <v>154</v>
-      </c>
-      <c r="D9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G9" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H9" t="s">
-        <v>131</v>
-      </c>
-      <c r="I9" t="s">
-        <v>134</v>
-      </c>
-      <c r="J9" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1080,31 +1128,31 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F10" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G10" s="1">
-        <v>45915</v>
+        <v>45701</v>
       </c>
       <c r="H10" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I10" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J10" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1112,31 +1160,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F11" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G11" s="1">
-        <v>44317</v>
+        <v>45538</v>
       </c>
       <c r="H11" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I11" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J11" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1144,31 +1192,31 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12">
-        <v>119</v>
+        <v>193</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="F12" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G12" s="1">
-        <v>45419</v>
+        <v>45915</v>
       </c>
       <c r="H12" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I12" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J12" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1176,31 +1224,31 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F13" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G13" s="1">
-        <v>44069</v>
+        <v>44317</v>
       </c>
       <c r="H13" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I13" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J13" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1208,31 +1256,31 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F14" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G14" s="1">
-        <v>44756</v>
+        <v>45419</v>
       </c>
       <c r="H14" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I14" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="J14" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1240,31 +1288,31 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G15" s="1">
-        <v>44348</v>
+        <v>44069</v>
       </c>
       <c r="H15" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I15" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="J15" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1272,31 +1320,31 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="F16" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G16" s="1">
-        <v>44452</v>
+        <v>44756</v>
       </c>
       <c r="H16" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I16" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="J16" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1304,31 +1352,31 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F17" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G17" s="1">
-        <v>45536</v>
+        <v>44348</v>
       </c>
       <c r="H17" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I17" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J17" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1336,31 +1384,31 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F18" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G18" s="1">
-        <v>44774</v>
+        <v>44452</v>
       </c>
       <c r="H18" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I18" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J18" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1368,31 +1416,31 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19">
-        <v>225</v>
+        <v>160</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="F19" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G19" s="1">
-        <v>46181</v>
+        <v>45536</v>
       </c>
       <c r="H19" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I19" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="J19" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1400,31 +1448,31 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20">
-        <v>227</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E20" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F20" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G20" s="1">
-        <v>46188</v>
+        <v>44774</v>
       </c>
       <c r="H20" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I20" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J20" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1432,31 +1480,31 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>225</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F21" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G21" s="1">
-        <v>43564</v>
+        <v>46181</v>
       </c>
       <c r="H21" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I21" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J21" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1464,31 +1512,31 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C22">
-        <v>168</v>
+        <v>227</v>
       </c>
       <c r="D22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E22" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="F22" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G22" s="1">
-        <v>46090</v>
+        <v>46188</v>
       </c>
       <c r="H22" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I22" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J22" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1496,31 +1544,31 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C23">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F23" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G23" s="1">
-        <v>44508</v>
+        <v>43564</v>
       </c>
       <c r="H23" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="I23" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J23" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1528,31 +1576,31 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24">
-        <v>60</v>
+        <v>168</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E24" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="F24" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G24" s="1">
-        <v>44774</v>
+        <v>46090</v>
       </c>
       <c r="H24" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I24" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J24" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1560,63 +1608,63 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E25" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="F25" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G25" s="1">
-        <v>45902</v>
+        <v>44508</v>
       </c>
       <c r="H25" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="I25" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="J25" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C26">
-        <v>77</v>
+        <v>1044</v>
       </c>
       <c r="D26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E26" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="F26" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G26" s="1">
-        <v>45047</v>
+        <v>45689</v>
       </c>
       <c r="H26" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I26" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="J26" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1624,31 +1672,31 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C27">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="D27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E27" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="F27" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G27" s="1">
-        <v>45859</v>
+        <v>44774</v>
       </c>
       <c r="H27" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I27" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J27" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1656,31 +1704,31 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C28">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="F28" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G28" s="1">
-        <v>45859</v>
+        <v>45902</v>
       </c>
       <c r="H28" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I28" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J28" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1688,31 +1736,31 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C29">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E29" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="F29" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G29" s="1">
-        <v>45809</v>
+        <v>45047</v>
       </c>
       <c r="H29" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I29" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="J29" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1720,63 +1768,63 @@
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C30">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="D30" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E30" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="F30" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G30" s="1">
-        <v>46017</v>
+        <v>45859</v>
       </c>
       <c r="H30" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I30" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J30" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>1037</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E31" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F31" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G31" s="1">
-        <v>45313</v>
+        <v>45512</v>
       </c>
       <c r="H31" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I31" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J31" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1784,31 +1832,31 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C32">
-        <v>58</v>
+        <v>183</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E32" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F32" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G32" s="1">
-        <v>44858</v>
+        <v>45859</v>
       </c>
       <c r="H32" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I32" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J32" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1816,31 +1864,31 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C33">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="F33" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G33" s="1">
-        <v>45600</v>
+        <v>45809</v>
       </c>
       <c r="H33" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I33" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="J33" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1848,31 +1896,31 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C34">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D34" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E34" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="F34" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G34" s="1">
-        <v>46113</v>
+        <v>46017</v>
       </c>
       <c r="H34" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I34" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J34" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -1880,31 +1928,31 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C35">
-        <v>212</v>
+        <v>5</v>
       </c>
       <c r="D35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="F35" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G35" s="1">
-        <v>46070</v>
+        <v>45313</v>
       </c>
       <c r="H35" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I35" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J35" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1912,31 +1960,31 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C36">
-        <v>226</v>
+        <v>58</v>
       </c>
       <c r="D36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E36" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F36" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G36" s="1">
-        <v>46181</v>
+        <v>44858</v>
       </c>
       <c r="H36" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I36" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="J36" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1944,31 +1992,31 @@
         <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C37">
-        <v>48</v>
+        <v>169</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E37" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F37" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G37" s="1">
-        <v>44348</v>
+        <v>45600</v>
       </c>
       <c r="H37" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I37" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J37" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -1976,31 +2024,31 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C38">
-        <v>122</v>
+        <v>207</v>
       </c>
       <c r="D38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F38" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G38" s="1">
-        <v>46126</v>
+        <v>46197</v>
       </c>
       <c r="H38" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I38" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2008,31 +2056,31 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C39">
-        <v>46</v>
+        <v>217</v>
       </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E39" t="s">
-        <v>30</v>
+        <v>116</v>
       </c>
       <c r="F39" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G39" s="1">
-        <v>44802</v>
+        <v>46113</v>
       </c>
       <c r="H39" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I39" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="J39" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2040,31 +2088,31 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C40">
-        <v>141</v>
+        <v>212</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E40" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F40" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G40" s="1">
-        <v>45499</v>
+        <v>46070</v>
       </c>
       <c r="H40" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I40" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J40" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2072,31 +2120,31 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C41">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E41" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F41" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G41" s="1">
-        <v>45957</v>
+        <v>46181</v>
       </c>
       <c r="H41" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I41" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J41" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2104,31 +2152,31 @@
         <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C42">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E42" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F42" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G42" s="1">
-        <v>43922</v>
+        <v>44348</v>
       </c>
       <c r="H42" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I42" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J42" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2136,31 +2184,31 @@
         <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C43">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="D43" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E43" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F43" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G43" s="1">
-        <v>45579</v>
+        <v>46126</v>
       </c>
       <c r="H43" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I43" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J43" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2168,31 +2216,31 @@
         <v>10</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C44">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="D44" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E44" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="F44" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G44" s="1">
-        <v>45509</v>
+        <v>44802</v>
       </c>
       <c r="H44" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I44" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J44" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2200,31 +2248,31 @@
         <v>10</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C45">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E45" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F45" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G45" s="1">
-        <v>46181</v>
+        <v>45499</v>
       </c>
       <c r="H45" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I45" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J45" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2232,31 +2280,31 @@
         <v>10</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C46">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="D46" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E46" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F46" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G46" s="1">
-        <v>46127</v>
+        <v>45957</v>
       </c>
       <c r="H46" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I46" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J46" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2264,31 +2312,31 @@
         <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C47">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E47" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F47" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G47" s="1">
-        <v>45778</v>
+        <v>43922</v>
       </c>
       <c r="H47" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I47" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="J47" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2296,31 +2344,31 @@
         <v>10</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C48">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="D48" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E48" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="F48" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G48" s="1">
-        <v>44537</v>
+        <v>45579</v>
       </c>
       <c r="H48" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I48" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J48" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -2328,63 +2376,63 @@
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C49">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D49" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E49" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F49" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G49" s="1">
-        <v>45531</v>
+        <v>45509</v>
       </c>
       <c r="H49" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I49" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J49" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C50">
-        <v>170</v>
+        <v>1028</v>
       </c>
       <c r="D50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E50" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F50" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G50" s="1">
-        <v>45600</v>
+        <v>45239</v>
       </c>
       <c r="H50" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I50" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J50" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2392,63 +2440,63 @@
         <v>10</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C51">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="D51" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E51" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="F51" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G51" s="1">
-        <v>45586</v>
+        <v>46181</v>
       </c>
       <c r="H51" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I51" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="J51" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C52">
-        <v>66</v>
+        <v>1043</v>
       </c>
       <c r="D52" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E52" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F52" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G52" s="1">
-        <v>44713</v>
+        <v>45680</v>
       </c>
       <c r="H52" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I52" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J52" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -2456,31 +2504,31 @@
         <v>10</v>
       </c>
       <c r="B53" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C53">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="D53" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E53" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F53" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G53" s="1">
-        <v>46048</v>
+        <v>46127</v>
       </c>
       <c r="H53" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I53" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J53" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -2488,31 +2536,31 @@
         <v>10</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C54">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="D54" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="E54" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F54" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G54" s="1">
-        <v>45243</v>
+        <v>45778</v>
       </c>
       <c r="H54" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I54" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J54" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -2520,31 +2568,31 @@
         <v>10</v>
       </c>
       <c r="B55" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C55">
-        <v>196</v>
+        <v>41</v>
       </c>
       <c r="D55" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E55" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F55" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G55" s="1">
-        <v>45924</v>
+        <v>44537</v>
       </c>
       <c r="H55" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I55" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J55" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -2552,31 +2600,31 @@
         <v>10</v>
       </c>
       <c r="B56" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C56">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D56" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="E56" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F56" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G56" s="1">
-        <v>45404</v>
+        <v>45531</v>
       </c>
       <c r="H56" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I56" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J56" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -2584,63 +2632,63 @@
         <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C57">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="D57" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="E57" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F57" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G57" s="1">
-        <v>46141</v>
+        <v>45600</v>
       </c>
       <c r="H57" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I57" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J57" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C58">
-        <v>223</v>
+        <v>1017</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E58" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F58" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G58" s="1">
-        <v>46163</v>
+        <v>45062</v>
       </c>
       <c r="H58" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="I58" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="J58" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -2648,63 +2696,63 @@
         <v>10</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C59">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="D59" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E59" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F59" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G59" s="1">
-        <v>45432</v>
+        <v>45586</v>
       </c>
       <c r="H59" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I59" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J59" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C60">
-        <v>210</v>
+        <v>1041</v>
       </c>
       <c r="D60" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E60" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="F60" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G60" s="1">
-        <v>46062</v>
+        <v>45689</v>
       </c>
       <c r="H60" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I60" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J60" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -2712,31 +2760,31 @@
         <v>10</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C61">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D61" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E61" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="F61" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G61" s="1">
-        <v>44909</v>
+        <v>44713</v>
       </c>
       <c r="H61" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I61" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="J61" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -2744,63 +2792,63 @@
         <v>10</v>
       </c>
       <c r="B62" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C62">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D62" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E62" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F62" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G62" s="1">
-        <v>45978</v>
+        <v>46048</v>
       </c>
       <c r="H62" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I62" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J62" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C63">
-        <v>199</v>
+        <v>1027</v>
       </c>
       <c r="D63" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E63" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F63" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G63" s="1">
-        <v>45938</v>
+        <v>45176</v>
       </c>
       <c r="H63" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I63" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J63" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -2808,31 +2856,31 @@
         <v>10</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C64">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="D64" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E64" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F64" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G64" s="1">
-        <v>46146</v>
+        <v>45243</v>
       </c>
       <c r="H64" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I64" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J64" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -2840,31 +2888,31 @@
         <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C65">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="D65" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E65" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F65" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G65" s="1">
-        <v>46076</v>
+        <v>45924</v>
       </c>
       <c r="H65" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I65" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J65" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -2872,63 +2920,63 @@
         <v>10</v>
       </c>
       <c r="B66" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C66">
-        <v>127</v>
+        <v>220</v>
       </c>
       <c r="D66" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="E66" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F66" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G66" s="1">
-        <v>45444</v>
+        <v>46141</v>
       </c>
       <c r="H66" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I66" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J66" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C67">
-        <v>214</v>
+        <v>1013</v>
       </c>
       <c r="D67" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E67" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F67" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G67" s="1">
-        <v>46076</v>
+        <v>44929</v>
       </c>
       <c r="H67" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I67" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J67" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -2936,31 +2984,31 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C68">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="D68" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E68" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="F68" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G68" s="1">
-        <v>45894</v>
+        <v>46163</v>
       </c>
       <c r="H68" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I68" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J68" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -2968,31 +3016,31 @@
         <v>10</v>
       </c>
       <c r="B69" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C69">
-        <v>9</v>
+        <v>121</v>
       </c>
       <c r="D69" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E69" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="F69" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G69" s="1">
-        <v>44287</v>
+        <v>45432</v>
       </c>
       <c r="H69" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I69" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J69" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -3000,31 +3048,31 @@
         <v>10</v>
       </c>
       <c r="B70" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C70">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D70" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E70" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="F70" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G70" s="1">
-        <v>45978</v>
+        <v>46062</v>
       </c>
       <c r="H70" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I70" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J70" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -3032,31 +3080,31 @@
         <v>10</v>
       </c>
       <c r="B71" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C71">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="D71" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E71" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F71" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G71" s="1">
-        <v>44683</v>
+        <v>44909</v>
       </c>
       <c r="H71" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I71" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J71" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3064,31 +3112,31 @@
         <v>10</v>
       </c>
       <c r="B72" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C72">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="D72" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E72" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="F72" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G72" s="1">
-        <v>46153</v>
+        <v>45978</v>
       </c>
       <c r="H72" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I72" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J72" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -3096,31 +3144,31 @@
         <v>10</v>
       </c>
       <c r="B73" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C73">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="D73" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E73" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="F73" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G73" s="1">
-        <v>45873</v>
+        <v>45938</v>
       </c>
       <c r="H73" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I73" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J73" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3128,31 +3176,31 @@
         <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C74">
-        <v>84</v>
+        <v>221</v>
       </c>
       <c r="D74" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E74" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F74" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G74" s="1">
-        <v>45121</v>
+        <v>46146</v>
       </c>
       <c r="H74" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I74" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J74" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -3160,31 +3208,31 @@
         <v>10</v>
       </c>
       <c r="B75" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C75">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="D75" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E75" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F75" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G75" s="1">
-        <v>45936</v>
+        <v>46076</v>
       </c>
       <c r="H75" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I75" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J75" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3192,63 +3240,447 @@
         <v>10</v>
       </c>
       <c r="B76" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C76">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D76" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E76" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F76" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G76" s="1">
-        <v>45957</v>
+        <v>45444</v>
       </c>
       <c r="H76" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="I76" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="J76" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C77">
+        <v>1008</v>
+      </c>
+      <c r="D77" t="s">
+        <v>84</v>
+      </c>
+      <c r="E77" t="s">
+        <v>139</v>
+      </c>
+      <c r="F77" t="s">
+        <v>145</v>
+      </c>
+      <c r="G77" s="1">
+        <v>46007</v>
+      </c>
+      <c r="H77" t="s">
+        <v>146</v>
+      </c>
+      <c r="I77" t="s">
+        <v>149</v>
+      </c>
+      <c r="J77" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" t="s">
+        <v>10</v>
+      </c>
+      <c r="B78" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78">
+        <v>214</v>
+      </c>
+      <c r="D78" t="s">
+        <v>85</v>
+      </c>
+      <c r="E78" t="s">
+        <v>139</v>
+      </c>
+      <c r="F78" t="s">
+        <v>145</v>
+      </c>
+      <c r="G78" s="1">
+        <v>46076</v>
+      </c>
+      <c r="H78" t="s">
+        <v>146</v>
+      </c>
+      <c r="I78" t="s">
+        <v>149</v>
+      </c>
+      <c r="J78" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" t="s">
+        <v>10</v>
+      </c>
+      <c r="B79" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79">
+        <v>229</v>
+      </c>
+      <c r="D79" t="s">
+        <v>86</v>
+      </c>
+      <c r="E79" t="s">
+        <v>140</v>
+      </c>
+      <c r="F79" t="s">
+        <v>145</v>
+      </c>
+      <c r="G79" s="1">
+        <v>46197</v>
+      </c>
+      <c r="H79" t="s">
+        <v>146</v>
+      </c>
+      <c r="I79" t="s">
+        <v>149</v>
+      </c>
+      <c r="J79" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" t="s">
+        <v>10</v>
+      </c>
+      <c r="B80" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80">
+        <v>189</v>
+      </c>
+      <c r="D80" t="s">
+        <v>87</v>
+      </c>
+      <c r="E80" t="s">
+        <v>140</v>
+      </c>
+      <c r="F80" t="s">
+        <v>145</v>
+      </c>
+      <c r="G80" s="1">
+        <v>45894</v>
+      </c>
+      <c r="H80" t="s">
+        <v>146</v>
+      </c>
+      <c r="I80" t="s">
+        <v>148</v>
+      </c>
+      <c r="J80" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" t="s">
+        <v>10</v>
+      </c>
+      <c r="B81" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81">
+        <v>9</v>
+      </c>
+      <c r="D81" t="s">
+        <v>88</v>
+      </c>
+      <c r="E81" t="s">
+        <v>141</v>
+      </c>
+      <c r="F81" t="s">
+        <v>145</v>
+      </c>
+      <c r="G81" s="1">
+        <v>44287</v>
+      </c>
+      <c r="H81" t="s">
+        <v>146</v>
+      </c>
+      <c r="I81" t="s">
+        <v>149</v>
+      </c>
+      <c r="J81" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" t="s">
+        <v>10</v>
+      </c>
+      <c r="B82" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82">
+        <v>204</v>
+      </c>
+      <c r="D82" t="s">
+        <v>89</v>
+      </c>
+      <c r="E82" t="s">
+        <v>141</v>
+      </c>
+      <c r="F82" t="s">
+        <v>145</v>
+      </c>
+      <c r="G82" s="1">
+        <v>45978</v>
+      </c>
+      <c r="H82" t="s">
+        <v>146</v>
+      </c>
+      <c r="I82" t="s">
+        <v>149</v>
+      </c>
+      <c r="J82" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" t="s">
+        <v>10</v>
+      </c>
+      <c r="B83" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83">
+        <v>22</v>
+      </c>
+      <c r="D83" t="s">
+        <v>90</v>
+      </c>
+      <c r="E83" t="s">
+        <v>141</v>
+      </c>
+      <c r="F83" t="s">
+        <v>145</v>
+      </c>
+      <c r="G83" s="1">
+        <v>44683</v>
+      </c>
+      <c r="H83" t="s">
+        <v>146</v>
+      </c>
+      <c r="I83" t="s">
+        <v>149</v>
+      </c>
+      <c r="J83" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" t="s">
+        <v>10</v>
+      </c>
+      <c r="B84" t="s">
+        <v>12</v>
+      </c>
+      <c r="C84">
+        <v>228</v>
+      </c>
+      <c r="D84" t="s">
+        <v>91</v>
+      </c>
+      <c r="E84" t="s">
+        <v>141</v>
+      </c>
+      <c r="F84" t="s">
+        <v>145</v>
+      </c>
+      <c r="G84" s="1">
+        <v>46153</v>
+      </c>
+      <c r="H84" t="s">
+        <v>146</v>
+      </c>
+      <c r="I84" t="s">
+        <v>148</v>
+      </c>
+      <c r="J84" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" t="s">
+        <v>10</v>
+      </c>
+      <c r="B85" t="s">
+        <v>12</v>
+      </c>
+      <c r="C85">
+        <v>187</v>
+      </c>
+      <c r="D85" t="s">
+        <v>92</v>
+      </c>
+      <c r="E85" t="s">
+        <v>141</v>
+      </c>
+      <c r="F85" t="s">
+        <v>145</v>
+      </c>
+      <c r="G85" s="1">
+        <v>45873</v>
+      </c>
+      <c r="H85" t="s">
+        <v>146</v>
+      </c>
+      <c r="I85" t="s">
+        <v>149</v>
+      </c>
+      <c r="J85" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" t="s">
+        <v>10</v>
+      </c>
+      <c r="B86" t="s">
+        <v>12</v>
+      </c>
+      <c r="C86">
+        <v>84</v>
+      </c>
+      <c r="D86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E86" t="s">
+        <v>142</v>
+      </c>
+      <c r="F86" t="s">
+        <v>145</v>
+      </c>
+      <c r="G86" s="1">
+        <v>45121</v>
+      </c>
+      <c r="H86" t="s">
+        <v>146</v>
+      </c>
+      <c r="I86" t="s">
+        <v>149</v>
+      </c>
+      <c r="J86" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" t="s">
+        <v>10</v>
+      </c>
+      <c r="B87" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87">
+        <v>198</v>
+      </c>
+      <c r="D87" t="s">
+        <v>94</v>
+      </c>
+      <c r="E87" t="s">
+        <v>142</v>
+      </c>
+      <c r="F87" t="s">
+        <v>145</v>
+      </c>
+      <c r="G87" s="1">
+        <v>45936</v>
+      </c>
+      <c r="H87" t="s">
+        <v>146</v>
+      </c>
+      <c r="I87" t="s">
+        <v>149</v>
+      </c>
+      <c r="J87" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" t="s">
+        <v>10</v>
+      </c>
+      <c r="B88" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88">
+        <v>133</v>
+      </c>
+      <c r="D88" t="s">
+        <v>95</v>
+      </c>
+      <c r="E88" t="s">
+        <v>143</v>
+      </c>
+      <c r="F88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G88" s="1">
+        <v>45957</v>
+      </c>
+      <c r="H88" t="s">
+        <v>146</v>
+      </c>
+      <c r="I88" t="s">
+        <v>149</v>
+      </c>
+      <c r="J88" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" t="s">
+        <v>10</v>
+      </c>
+      <c r="B89" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89">
         <v>3</v>
       </c>
-      <c r="D77" t="s">
-        <v>82</v>
-      </c>
-      <c r="E77" t="s">
-        <v>129</v>
-      </c>
-      <c r="F77" t="s">
-        <v>130</v>
-      </c>
-      <c r="G77" s="1">
+      <c r="D89" t="s">
+        <v>96</v>
+      </c>
+      <c r="E89" t="s">
+        <v>144</v>
+      </c>
+      <c r="F89" t="s">
+        <v>145</v>
+      </c>
+      <c r="G89" s="1">
         <v>44348</v>
       </c>
-      <c r="H77" t="s">
-        <v>131</v>
-      </c>
-      <c r="I77" t="s">
-        <v>134</v>
-      </c>
-      <c r="J77" t="s">
-        <v>141</v>
+      <c r="H89" t="s">
+        <v>146</v>
+      </c>
+      <c r="I89" t="s">
+        <v>149</v>
+      </c>
+      <c r="J89" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/employees_CA.xlsx
+++ b/employees_CA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="160">
   <si>
     <t>Legal Name</t>
   </si>
@@ -58,246 +58,255 @@
     <t>Kun</t>
   </si>
   <si>
+    <t>Xinyi</t>
+  </si>
+  <si>
+    <t>Hong</t>
+  </si>
+  <si>
+    <t>Jian</t>
+  </si>
+  <si>
+    <t>Zhenjun</t>
+  </si>
+  <si>
+    <t>Qingzi</t>
+  </si>
+  <si>
+    <t>Weixia</t>
+  </si>
+  <si>
+    <t>Xiaolong</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>Huali</t>
+  </si>
+  <si>
+    <t>Yankun</t>
+  </si>
+  <si>
+    <t>Ya-Mei</t>
+  </si>
+  <si>
+    <t>Hui</t>
+  </si>
+  <si>
+    <t>Aixin</t>
+  </si>
+  <si>
+    <t>Bin</t>
+  </si>
+  <si>
+    <t>Chunpeng</t>
+  </si>
+  <si>
+    <t>Bing</t>
+  </si>
+  <si>
+    <t>Xixing</t>
+  </si>
+  <si>
+    <t>Wenhu</t>
+  </si>
+  <si>
+    <t>Enquan</t>
+  </si>
+  <si>
+    <t>Lixin</t>
+  </si>
+  <si>
+    <t>Ting</t>
+  </si>
+  <si>
+    <t>KunIengCheong</t>
+  </si>
+  <si>
+    <t>Enduo</t>
+  </si>
+  <si>
+    <t>Guanzhong</t>
+  </si>
+  <si>
+    <t>Jie</t>
+  </si>
+  <si>
+    <t>Zhihong</t>
+  </si>
+  <si>
+    <t>Yaodong</t>
+  </si>
+  <si>
+    <t>Chunyang</t>
+  </si>
+  <si>
+    <t>Emily</t>
+  </si>
+  <si>
+    <t>Jing</t>
+  </si>
+  <si>
+    <t>Xiaoyang</t>
+  </si>
+  <si>
+    <t>Xin</t>
+  </si>
+  <si>
+    <t>Yinli</t>
+  </si>
+  <si>
+    <t>Arze</t>
+  </si>
+  <si>
+    <t>HAIBO</t>
+  </si>
+  <si>
+    <t>Yuwei</t>
+  </si>
+  <si>
+    <t>Boyu</t>
+  </si>
+  <si>
+    <t>Zhiyi</t>
+  </si>
+  <si>
+    <t>Guillermo F</t>
+  </si>
+  <si>
+    <t>Huanyu</t>
+  </si>
+  <si>
+    <t>Guanqi</t>
+  </si>
+  <si>
+    <t>Jaime</t>
+  </si>
+  <si>
+    <t>Yinghui</t>
+  </si>
+  <si>
+    <t>Wingking</t>
+  </si>
+  <si>
+    <t>Tip Wa</t>
+  </si>
+  <si>
+    <t>Yi</t>
+  </si>
+  <si>
+    <t>CaiChin</t>
+  </si>
+  <si>
+    <t>Jiayu</t>
+  </si>
+  <si>
+    <t>Weidong</t>
+  </si>
+  <si>
+    <t>Libang</t>
+  </si>
+  <si>
+    <t>Jiran</t>
+  </si>
+  <si>
+    <t>Ya-Han</t>
+  </si>
+  <si>
+    <t>Zhen</t>
+  </si>
+  <si>
+    <t>Xinyuan</t>
+  </si>
+  <si>
+    <t>Guang</t>
+  </si>
+  <si>
+    <t>Ming</t>
+  </si>
+  <si>
+    <t>Xurong</t>
+  </si>
+  <si>
+    <t>Yihui</t>
+  </si>
+  <si>
+    <t>Yiyu</t>
+  </si>
+  <si>
+    <t>Yuran</t>
+  </si>
+  <si>
+    <t>Huan</t>
+  </si>
+  <si>
+    <t>Qianyang</t>
+  </si>
+  <si>
+    <t>Gang</t>
+  </si>
+  <si>
+    <t>Haiqiang</t>
+  </si>
+  <si>
+    <t>Jinping</t>
+  </si>
+  <si>
+    <t>Xiaqing</t>
+  </si>
+  <si>
+    <t>Yuhua</t>
+  </si>
+  <si>
+    <t>Xidong</t>
+  </si>
+  <si>
+    <t>Yalin</t>
+  </si>
+  <si>
+    <t>Minlin</t>
+  </si>
+  <si>
+    <t>Changqing</t>
+  </si>
+  <si>
     <t>David</t>
   </si>
   <si>
-    <t>Hong</t>
-  </si>
-  <si>
-    <t>Jian</t>
-  </si>
-  <si>
     <t>Ye</t>
   </si>
   <si>
-    <t>Zhenjun</t>
-  </si>
-  <si>
-    <t>Qingzi</t>
-  </si>
-  <si>
-    <t>Weixia</t>
-  </si>
-  <si>
-    <t>Anna</t>
-  </si>
-  <si>
-    <t>Huali</t>
-  </si>
-  <si>
-    <t>Yankun</t>
-  </si>
-  <si>
-    <t>Ya-Mei</t>
-  </si>
-  <si>
-    <t>Hui</t>
-  </si>
-  <si>
-    <t>Aixin</t>
-  </si>
-  <si>
-    <t>Bin</t>
-  </si>
-  <si>
-    <t>Chunpeng</t>
-  </si>
-  <si>
-    <t>Bing</t>
-  </si>
-  <si>
-    <t>Xixing</t>
-  </si>
-  <si>
-    <t>Wenhu</t>
-  </si>
-  <si>
-    <t>Enquan</t>
-  </si>
-  <si>
-    <t>Lixin</t>
-  </si>
-  <si>
-    <t>Ting</t>
-  </si>
-  <si>
     <t>Jiu</t>
   </si>
   <si>
-    <t>KunIengCheong</t>
-  </si>
-  <si>
-    <t>Enduo</t>
-  </si>
-  <si>
-    <t>Guanzhong</t>
-  </si>
-  <si>
-    <t>Jie</t>
-  </si>
-  <si>
-    <t>Zhihong</t>
-  </si>
-  <si>
-    <t>Yaodong</t>
-  </si>
-  <si>
-    <t>Chunyang</t>
-  </si>
-  <si>
-    <t>Emily</t>
-  </si>
-  <si>
-    <t>Jing</t>
-  </si>
-  <si>
-    <t>Xiaoyang</t>
-  </si>
-  <si>
-    <t>Xin</t>
-  </si>
-  <si>
-    <t>Yinli</t>
-  </si>
-  <si>
-    <t>Arze</t>
-  </si>
-  <si>
-    <t>HAIBO</t>
-  </si>
-  <si>
-    <t>Yuwei</t>
-  </si>
-  <si>
-    <t>Boyu</t>
-  </si>
-  <si>
-    <t>Zhiyi</t>
-  </si>
-  <si>
-    <t>Guillermo F</t>
-  </si>
-  <si>
-    <t>Huanyu</t>
-  </si>
-  <si>
-    <t>Guanqi</t>
-  </si>
-  <si>
-    <t>Jaime</t>
-  </si>
-  <si>
     <t>Lanlan</t>
   </si>
   <si>
-    <t>Yinghui</t>
-  </si>
-  <si>
     <t>Zhaoyi</t>
   </si>
   <si>
-    <t>Wingking</t>
-  </si>
-  <si>
-    <t>Tip Wa</t>
-  </si>
-  <si>
-    <t>Yi</t>
-  </si>
-  <si>
-    <t>CaiChin</t>
-  </si>
-  <si>
-    <t>Jiayu</t>
-  </si>
-  <si>
     <t>Ying</t>
   </si>
   <si>
-    <t>Weidong</t>
-  </si>
-  <si>
     <t>Lexi</t>
   </si>
   <si>
-    <t>Libang</t>
-  </si>
-  <si>
     <t>Yujian</t>
   </si>
   <si>
-    <t>Jiran</t>
-  </si>
-  <si>
     <t>Xiangju</t>
   </si>
   <si>
-    <t>Ya-Han</t>
-  </si>
-  <si>
-    <t>Zhen</t>
-  </si>
-  <si>
-    <t>Xinyuan</t>
-  </si>
-  <si>
-    <t>Guang</t>
-  </si>
-  <si>
-    <t>Ming</t>
-  </si>
-  <si>
-    <t>Xurong</t>
-  </si>
-  <si>
-    <t>Yihui</t>
-  </si>
-  <si>
-    <t>Yiyu</t>
-  </si>
-  <si>
     <t>Yue</t>
   </si>
   <si>
-    <t>Yuran</t>
-  </si>
-  <si>
-    <t>Huan</t>
-  </si>
-  <si>
-    <t>Qianyang</t>
-  </si>
-  <si>
-    <t>Gang</t>
-  </si>
-  <si>
-    <t>Haiqiang</t>
-  </si>
-  <si>
-    <t>Jinping</t>
-  </si>
-  <si>
-    <t>Xiaqing</t>
-  </si>
-  <si>
-    <t>Yuhua</t>
-  </si>
-  <si>
-    <t>Xidong</t>
-  </si>
-  <si>
-    <t>Yalin</t>
-  </si>
-  <si>
-    <t>Minlin</t>
-  </si>
-  <si>
-    <t>Changqing</t>
-  </si>
-  <si>
     <t>Bian</t>
   </si>
   <si>
+    <t>Cai</t>
+  </si>
+  <si>
     <t>Chen</t>
   </si>
   <si>
@@ -307,6 +316,9 @@
     <t>Cui</t>
   </si>
   <si>
+    <t>Deng</t>
+  </si>
+  <si>
     <t>Duan</t>
   </si>
   <si>
@@ -400,42 +412,42 @@
     <t>Wei</t>
   </si>
   <si>
+    <t>Xia</t>
+  </si>
+  <si>
+    <t>Xu</t>
+  </si>
+  <si>
+    <t>Yang</t>
+  </si>
+  <si>
+    <t>Yu</t>
+  </si>
+  <si>
+    <t>Zhang</t>
+  </si>
+  <si>
+    <t>Zhao</t>
+  </si>
+  <si>
+    <t>Zheng</t>
+  </si>
+  <si>
+    <t>Zhou</t>
+  </si>
+  <si>
+    <t>Zhuang</t>
+  </si>
+  <si>
+    <t>Zou</t>
+  </si>
+  <si>
     <t>Winstone</t>
   </si>
   <si>
-    <t>Xia</t>
-  </si>
-  <si>
     <t>Xiong</t>
   </si>
   <si>
-    <t>Xu</t>
-  </si>
-  <si>
-    <t>Yang</t>
-  </si>
-  <si>
-    <t>Yu</t>
-  </si>
-  <si>
-    <t>Zhang</t>
-  </si>
-  <si>
-    <t>Zhao</t>
-  </si>
-  <si>
-    <t>Zheng</t>
-  </si>
-  <si>
-    <t>Zhou</t>
-  </si>
-  <si>
-    <t>Zhuang</t>
-  </si>
-  <si>
-    <t>Zou</t>
-  </si>
-  <si>
     <t>Active</t>
   </si>
   <si>
@@ -454,34 +466,34 @@
     <t>Executive - Executive</t>
   </si>
   <si>
+    <t>Transfer - Transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unloading - Unloading </t>
+  </si>
+  <si>
+    <t>HR - HR</t>
+  </si>
+  <si>
+    <t>QC - QC</t>
+  </si>
+  <si>
+    <t>Shipping - Shipping</t>
+  </si>
+  <si>
+    <t>Accounting - Accounting</t>
+  </si>
+  <si>
+    <t>Dispatch - Dispatching Center</t>
+  </si>
+  <si>
+    <t>Resource - Resource Center</t>
+  </si>
+  <si>
+    <t>Commerce - Commerce Department</t>
+  </si>
+  <si>
     <t>Drop-Shipp - Drop-Shipping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unloading - Unloading </t>
-  </si>
-  <si>
-    <t>HR - HR</t>
-  </si>
-  <si>
-    <t>Transfer - Transfer</t>
-  </si>
-  <si>
-    <t>QC - QC</t>
-  </si>
-  <si>
-    <t>Accounting - Accounting</t>
-  </si>
-  <si>
-    <t>Shipping - Shipping</t>
-  </si>
-  <si>
-    <t>Dispatch - Dispatching Center</t>
-  </si>
-  <si>
-    <t>Resource - Resource Center</t>
-  </si>
-  <si>
-    <t>Commerce - Commerce Department</t>
   </si>
 </sst>
 </file>
@@ -817,7 +829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -866,54 +878,54 @@
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G2" s="1">
         <v>45916</v>
       </c>
       <c r="H2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3">
-        <v>1012</v>
+        <v>232</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G3" s="1">
-        <v>44929</v>
+        <v>46230</v>
       </c>
       <c r="H3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -930,22 +942,22 @@
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G4" s="1">
         <v>46168</v>
       </c>
       <c r="H4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -962,54 +974,54 @@
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G5" s="1">
         <v>43405</v>
       </c>
       <c r="H5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6">
-        <v>1040</v>
+        <v>191</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G6" s="1">
-        <v>45684</v>
+        <v>45909</v>
       </c>
       <c r="H6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I6" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1020,28 +1032,28 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>191</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G7" s="1">
-        <v>45909</v>
+        <v>45471</v>
       </c>
       <c r="H7" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1052,25 +1064,25 @@
         <v>12</v>
       </c>
       <c r="C8">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D8" t="s">
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G8" s="1">
-        <v>45471</v>
+        <v>45701</v>
       </c>
       <c r="H8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I8" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J8" t="s">
         <v>150</v>
@@ -1084,28 +1096,28 @@
         <v>12</v>
       </c>
       <c r="C9">
-        <v>174</v>
+        <v>231</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G9" s="1">
-        <v>45701</v>
+        <v>46225</v>
       </c>
       <c r="H9" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I9" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J9" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1122,22 +1134,22 @@
         <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G10" s="1">
         <v>45538</v>
       </c>
       <c r="H10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1154,22 +1166,22 @@
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F11" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G11" s="1">
         <v>45915</v>
       </c>
       <c r="H11" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1186,22 +1198,22 @@
         <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F12" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G12" s="1">
         <v>44317</v>
       </c>
       <c r="H12" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I12" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1218,22 +1230,22 @@
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F13" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G13" s="1">
         <v>45419</v>
       </c>
       <c r="H13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J13" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1250,22 +1262,22 @@
         <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G14" s="1">
         <v>44069</v>
       </c>
       <c r="H14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I14" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1282,22 +1294,22 @@
         <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F15" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G15" s="1">
         <v>44756</v>
       </c>
       <c r="H15" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I15" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J15" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1314,22 +1326,22 @@
         <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F16" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G16" s="1">
         <v>44348</v>
       </c>
       <c r="H16" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J16" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1346,22 +1358,22 @@
         <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F17" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G17" s="1">
         <v>44452</v>
       </c>
       <c r="H17" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I17" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1378,22 +1390,22 @@
         <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F18" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G18" s="1">
         <v>45536</v>
       </c>
       <c r="H18" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I18" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J18" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1410,22 +1422,22 @@
         <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F19" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G19" s="1">
         <v>44774</v>
       </c>
       <c r="H19" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I19" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1442,22 +1454,22 @@
         <v>31</v>
       </c>
       <c r="E20" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F20" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G20" s="1">
         <v>46181</v>
       </c>
       <c r="H20" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I20" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J20" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1474,22 +1486,22 @@
         <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F21" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G21" s="1">
         <v>43564</v>
       </c>
       <c r="H21" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I21" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J21" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1506,22 +1518,22 @@
         <v>33</v>
       </c>
       <c r="E22" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F22" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G22" s="1">
         <v>46090</v>
       </c>
       <c r="H22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I22" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J22" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1538,54 +1550,54 @@
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F23" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G23" s="1">
         <v>44508</v>
       </c>
       <c r="H23" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I23" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J23" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
       </c>
       <c r="C24">
-        <v>1044</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
         <v>35</v>
       </c>
       <c r="E24" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="F24" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G24" s="1">
-        <v>45689</v>
+        <v>44774</v>
       </c>
       <c r="H24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I24" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1596,28 +1608,28 @@
         <v>12</v>
       </c>
       <c r="C25">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="D25" t="s">
         <v>36</v>
       </c>
       <c r="E25" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F25" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G25" s="1">
-        <v>44774</v>
+        <v>45902</v>
       </c>
       <c r="H25" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I25" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J25" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1628,28 +1640,28 @@
         <v>12</v>
       </c>
       <c r="C26">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s">
         <v>37</v>
       </c>
       <c r="E26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F26" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G26" s="1">
-        <v>45902</v>
+        <v>45047</v>
       </c>
       <c r="H26" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I26" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J26" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1660,28 +1672,28 @@
         <v>12</v>
       </c>
       <c r="C27">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="D27" t="s">
         <v>38</v>
       </c>
       <c r="E27" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F27" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G27" s="1">
-        <v>45047</v>
+        <v>45859</v>
       </c>
       <c r="H27" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I27" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J27" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1692,28 +1704,28 @@
         <v>12</v>
       </c>
       <c r="C28">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D28" t="s">
         <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F28" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G28" s="1">
         <v>45859</v>
       </c>
       <c r="H28" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J28" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1724,28 +1736,28 @@
         <v>12</v>
       </c>
       <c r="C29">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D29" t="s">
         <v>40</v>
       </c>
       <c r="E29" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F29" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G29" s="1">
-        <v>45859</v>
+        <v>45809</v>
       </c>
       <c r="H29" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I29" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J29" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1756,28 +1768,28 @@
         <v>12</v>
       </c>
       <c r="C30">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="D30" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F30" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G30" s="1">
-        <v>45809</v>
+        <v>46017</v>
       </c>
       <c r="H30" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I30" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J30" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1788,28 +1800,28 @@
         <v>12</v>
       </c>
       <c r="C31">
-        <v>208</v>
+        <v>5</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E31" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F31" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G31" s="1">
-        <v>46017</v>
+        <v>45313</v>
       </c>
       <c r="H31" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J31" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1820,28 +1832,28 @@
         <v>12</v>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="D32" t="s">
         <v>42</v>
       </c>
       <c r="E32" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F32" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G32" s="1">
-        <v>45313</v>
+        <v>44858</v>
       </c>
       <c r="H32" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I32" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J32" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1852,28 +1864,28 @@
         <v>12</v>
       </c>
       <c r="C33">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="D33" t="s">
         <v>43</v>
       </c>
       <c r="E33" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F33" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G33" s="1">
-        <v>44858</v>
+        <v>45600</v>
       </c>
       <c r="H33" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I33" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J33" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1884,28 +1896,28 @@
         <v>12</v>
       </c>
       <c r="C34">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="D34" t="s">
         <v>44</v>
       </c>
       <c r="E34" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F34" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G34" s="1">
-        <v>45600</v>
+        <v>46197</v>
       </c>
       <c r="H34" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I34" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J34" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -1916,28 +1928,28 @@
         <v>12</v>
       </c>
       <c r="C35">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="D35" t="s">
         <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F35" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G35" s="1">
-        <v>46197</v>
+        <v>46113</v>
       </c>
       <c r="H35" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I35" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J35" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1948,28 +1960,28 @@
         <v>12</v>
       </c>
       <c r="C36">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D36" t="s">
         <v>46</v>
       </c>
       <c r="E36" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G36" s="1">
-        <v>46113</v>
+        <v>46070</v>
       </c>
       <c r="H36" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I36" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J36" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1980,28 +1992,28 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="D37" t="s">
         <v>47</v>
       </c>
       <c r="E37" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F37" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G37" s="1">
-        <v>46070</v>
+        <v>46181</v>
       </c>
       <c r="H37" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I37" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J37" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2012,28 +2024,28 @@
         <v>12</v>
       </c>
       <c r="C38">
-        <v>226</v>
+        <v>48</v>
       </c>
       <c r="D38" t="s">
         <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F38" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G38" s="1">
-        <v>46181</v>
+        <v>44348</v>
       </c>
       <c r="H38" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I38" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J38" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2044,28 +2056,28 @@
         <v>12</v>
       </c>
       <c r="C39">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="D39" t="s">
         <v>49</v>
       </c>
       <c r="E39" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F39" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G39" s="1">
-        <v>44348</v>
+        <v>46126</v>
       </c>
       <c r="H39" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I39" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J39" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2076,28 +2088,28 @@
         <v>12</v>
       </c>
       <c r="C40">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="D40" t="s">
         <v>50</v>
       </c>
       <c r="E40" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F40" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G40" s="1">
-        <v>46126</v>
+        <v>44802</v>
       </c>
       <c r="H40" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I40" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J40" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2108,28 +2120,28 @@
         <v>12</v>
       </c>
       <c r="C41">
-        <v>46</v>
+        <v>141</v>
       </c>
       <c r="D41" t="s">
         <v>51</v>
       </c>
       <c r="E41" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F41" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G41" s="1">
-        <v>44802</v>
+        <v>45499</v>
       </c>
       <c r="H41" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I41" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J41" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2140,25 +2152,25 @@
         <v>12</v>
       </c>
       <c r="C42">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="D42" t="s">
         <v>52</v>
       </c>
       <c r="E42" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F42" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G42" s="1">
-        <v>45499</v>
+        <v>45957</v>
       </c>
       <c r="H42" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I42" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J42" t="s">
         <v>154</v>
@@ -2172,28 +2184,28 @@
         <v>12</v>
       </c>
       <c r="C43">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="D43" t="s">
         <v>53</v>
       </c>
       <c r="E43" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F43" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G43" s="1">
-        <v>45957</v>
+        <v>43922</v>
       </c>
       <c r="H43" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I43" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2204,28 +2216,28 @@
         <v>12</v>
       </c>
       <c r="C44">
-        <v>15</v>
+        <v>165</v>
       </c>
       <c r="D44" t="s">
         <v>54</v>
       </c>
       <c r="E44" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F44" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G44" s="1">
-        <v>43922</v>
+        <v>45579</v>
       </c>
       <c r="H44" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I44" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J44" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2236,28 +2248,28 @@
         <v>12</v>
       </c>
       <c r="C45">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D45" t="s">
         <v>55</v>
       </c>
       <c r="E45" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F45" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G45" s="1">
-        <v>45579</v>
+        <v>45509</v>
       </c>
       <c r="H45" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I45" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J45" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2268,60 +2280,60 @@
         <v>12</v>
       </c>
       <c r="C46">
-        <v>147</v>
+        <v>85</v>
       </c>
       <c r="D46" t="s">
         <v>56</v>
       </c>
       <c r="E46" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F46" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G46" s="1">
-        <v>45509</v>
+        <v>46181</v>
       </c>
       <c r="H46" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I46" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J46" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
       </c>
       <c r="C47">
-        <v>1028</v>
+        <v>218</v>
       </c>
       <c r="D47" t="s">
         <v>57</v>
       </c>
       <c r="E47" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F47" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G47" s="1">
-        <v>45239</v>
+        <v>46127</v>
       </c>
       <c r="H47" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I47" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J47" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2332,60 +2344,60 @@
         <v>12</v>
       </c>
       <c r="C48">
-        <v>85</v>
+        <v>176</v>
       </c>
       <c r="D48" t="s">
         <v>58</v>
       </c>
       <c r="E48" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F48" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G48" s="1">
-        <v>46181</v>
+        <v>45778</v>
       </c>
       <c r="H48" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I48" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J48" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
       </c>
       <c r="C49">
-        <v>1043</v>
+        <v>41</v>
       </c>
       <c r="D49" t="s">
         <v>59</v>
       </c>
       <c r="E49" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F49" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G49" s="1">
-        <v>45680</v>
+        <v>44537</v>
       </c>
       <c r="H49" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I49" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J49" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -2396,28 +2408,28 @@
         <v>12</v>
       </c>
       <c r="C50">
-        <v>218</v>
+        <v>151</v>
       </c>
       <c r="D50" t="s">
         <v>60</v>
       </c>
       <c r="E50" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F50" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G50" s="1">
-        <v>46127</v>
+        <v>45531</v>
       </c>
       <c r="H50" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I50" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J50" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2428,28 +2440,28 @@
         <v>12</v>
       </c>
       <c r="C51">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D51" t="s">
         <v>61</v>
       </c>
       <c r="E51" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F51" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G51" s="1">
-        <v>45778</v>
+        <v>45600</v>
       </c>
       <c r="H51" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I51" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J51" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -2460,28 +2472,28 @@
         <v>12</v>
       </c>
       <c r="C52">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c r="D52" t="s">
         <v>62</v>
       </c>
       <c r="E52" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F52" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G52" s="1">
-        <v>44537</v>
+        <v>45586</v>
       </c>
       <c r="H52" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I52" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J52" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -2492,28 +2504,28 @@
         <v>12</v>
       </c>
       <c r="C53">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="D53" t="s">
         <v>63</v>
       </c>
       <c r="E53" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F53" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G53" s="1">
-        <v>45531</v>
+        <v>46048</v>
       </c>
       <c r="H53" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I53" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J53" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -2524,60 +2536,60 @@
         <v>12</v>
       </c>
       <c r="C54">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="D54" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="E54" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F54" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G54" s="1">
-        <v>45600</v>
+        <v>45243</v>
       </c>
       <c r="H54" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I54" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J54" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
       </c>
       <c r="C55">
-        <v>1017</v>
+        <v>196</v>
       </c>
       <c r="D55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E55" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F55" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G55" s="1">
-        <v>45062</v>
+        <v>45924</v>
       </c>
       <c r="H55" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I55" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J55" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -2588,60 +2600,60 @@
         <v>12</v>
       </c>
       <c r="C56">
-        <v>166</v>
+        <v>220</v>
       </c>
       <c r="D56" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="E56" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="F56" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G56" s="1">
-        <v>45586</v>
+        <v>46141</v>
       </c>
       <c r="H56" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I56" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J56" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
       </c>
       <c r="C57">
-        <v>1041</v>
+        <v>223</v>
       </c>
       <c r="D57" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E57" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F57" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G57" s="1">
-        <v>45689</v>
+        <v>46163</v>
       </c>
       <c r="H57" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I57" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J57" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -2652,60 +2664,60 @@
         <v>12</v>
       </c>
       <c r="C58">
-        <v>209</v>
+        <v>121</v>
       </c>
       <c r="D58" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E58" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F58" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G58" s="1">
-        <v>46048</v>
+        <v>45432</v>
       </c>
       <c r="H58" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I58" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J58" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
       </c>
       <c r="C59">
-        <v>1027</v>
+        <v>210</v>
       </c>
       <c r="D59" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E59" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="F59" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G59" s="1">
-        <v>45176</v>
+        <v>46062</v>
       </c>
       <c r="H59" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I59" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J59" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -2716,28 +2728,28 @@
         <v>12</v>
       </c>
       <c r="C60">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D60" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="E60" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F60" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G60" s="1">
-        <v>45243</v>
+        <v>44909</v>
       </c>
       <c r="H60" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I60" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J60" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -2748,28 +2760,28 @@
         <v>12</v>
       </c>
       <c r="C61">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E61" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F61" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G61" s="1">
-        <v>45924</v>
+        <v>45978</v>
       </c>
       <c r="H61" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I61" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J61" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -2780,25 +2792,25 @@
         <v>12</v>
       </c>
       <c r="C62">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="D62" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="E62" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F62" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G62" s="1">
-        <v>46141</v>
+        <v>45938</v>
       </c>
       <c r="H62" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I62" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J62" t="s">
         <v>151</v>
@@ -2806,34 +2818,34 @@
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
       </c>
       <c r="C63">
-        <v>1013</v>
+        <v>221</v>
       </c>
       <c r="D63" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E63" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F63" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G63" s="1">
-        <v>44929</v>
+        <v>46146</v>
       </c>
       <c r="H63" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I63" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J63" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -2844,28 +2856,28 @@
         <v>12</v>
       </c>
       <c r="C64">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="D64" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E64" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F64" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G64" s="1">
-        <v>46163</v>
+        <v>46076</v>
       </c>
       <c r="H64" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I64" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J64" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -2876,28 +2888,28 @@
         <v>12</v>
       </c>
       <c r="C65">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D65" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E65" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F65" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G65" s="1">
-        <v>45432</v>
+        <v>45444</v>
       </c>
       <c r="H65" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I65" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J65" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -2908,28 +2920,28 @@
         <v>12</v>
       </c>
       <c r="C66">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E66" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F66" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G66" s="1">
-        <v>46062</v>
+        <v>46076</v>
       </c>
       <c r="H66" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I66" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J66" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -2940,28 +2952,28 @@
         <v>12</v>
       </c>
       <c r="C67">
-        <v>65</v>
+        <v>229</v>
       </c>
       <c r="D67" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E67" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F67" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G67" s="1">
-        <v>44909</v>
+        <v>46197</v>
       </c>
       <c r="H67" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I67" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J67" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -2972,28 +2984,28 @@
         <v>12</v>
       </c>
       <c r="C68">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E68" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F68" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G68" s="1">
-        <v>45978</v>
+        <v>45894</v>
       </c>
       <c r="H68" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I68" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J68" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -3004,28 +3016,28 @@
         <v>12</v>
       </c>
       <c r="C69">
-        <v>199</v>
+        <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E69" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F69" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G69" s="1">
-        <v>45938</v>
+        <v>44287</v>
       </c>
       <c r="H69" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I69" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J69" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -3036,25 +3048,25 @@
         <v>12</v>
       </c>
       <c r="C70">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="D70" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E70" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F70" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G70" s="1">
-        <v>46146</v>
+        <v>45978</v>
       </c>
       <c r="H70" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I70" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J70" t="s">
         <v>154</v>
@@ -3068,28 +3080,28 @@
         <v>12</v>
       </c>
       <c r="C71">
-        <v>213</v>
+        <v>22</v>
       </c>
       <c r="D71" t="s">
         <v>78</v>
       </c>
       <c r="E71" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F71" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G71" s="1">
-        <v>46076</v>
+        <v>44683</v>
       </c>
       <c r="H71" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I71" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J71" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3100,60 +3112,60 @@
         <v>12</v>
       </c>
       <c r="C72">
-        <v>127</v>
+        <v>228</v>
       </c>
       <c r="D72" t="s">
         <v>79</v>
       </c>
       <c r="E72" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F72" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G72" s="1">
-        <v>45444</v>
+        <v>46153</v>
       </c>
       <c r="H72" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I72" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J72" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
       </c>
       <c r="C73">
-        <v>1008</v>
+        <v>187</v>
       </c>
       <c r="D73" t="s">
         <v>80</v>
       </c>
       <c r="E73" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F73" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G73" s="1">
-        <v>46007</v>
+        <v>45873</v>
       </c>
       <c r="H73" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I73" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J73" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3164,28 +3176,28 @@
         <v>12</v>
       </c>
       <c r="C74">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="D74" t="s">
         <v>81</v>
       </c>
       <c r="E74" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F74" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G74" s="1">
-        <v>46076</v>
+        <v>45121</v>
       </c>
       <c r="H74" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I74" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J74" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -3196,28 +3208,28 @@
         <v>12</v>
       </c>
       <c r="C75">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="D75" t="s">
         <v>82</v>
       </c>
       <c r="E75" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F75" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G75" s="1">
-        <v>46197</v>
+        <v>45936</v>
       </c>
       <c r="H75" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I75" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J75" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3228,28 +3240,28 @@
         <v>12</v>
       </c>
       <c r="C76">
-        <v>189</v>
+        <v>133</v>
       </c>
       <c r="D76" t="s">
         <v>83</v>
       </c>
       <c r="E76" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F76" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G76" s="1">
-        <v>45894</v>
+        <v>45957</v>
       </c>
       <c r="H76" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I76" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J76" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3260,284 +3272,348 @@
         <v>12</v>
       </c>
       <c r="C77">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D77" t="s">
         <v>84</v>
       </c>
       <c r="E77" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F77" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G77" s="1">
-        <v>44287</v>
+        <v>44348</v>
       </c>
       <c r="H77" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I77" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J77" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B78" t="s">
         <v>12</v>
       </c>
       <c r="C78">
-        <v>204</v>
+        <v>1012</v>
       </c>
       <c r="D78" t="s">
         <v>85</v>
       </c>
       <c r="E78" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="F78" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G78" s="1">
-        <v>45978</v>
+        <v>44929</v>
       </c>
       <c r="H78" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I78" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J78" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
       </c>
       <c r="C79">
-        <v>22</v>
+        <v>1040</v>
       </c>
       <c r="D79" t="s">
         <v>86</v>
       </c>
       <c r="E79" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="F79" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G79" s="1">
-        <v>44683</v>
+        <v>45684</v>
       </c>
       <c r="H79" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I79" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J79" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B80" t="s">
         <v>12</v>
       </c>
       <c r="C80">
-        <v>228</v>
+        <v>1044</v>
       </c>
       <c r="D80" t="s">
         <v>87</v>
       </c>
       <c r="E80" t="s">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="F80" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G80" s="1">
-        <v>46153</v>
+        <v>45689</v>
       </c>
       <c r="H80" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I80" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J80" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B81" t="s">
         <v>12</v>
       </c>
       <c r="C81">
-        <v>187</v>
+        <v>1028</v>
       </c>
       <c r="D81" t="s">
         <v>88</v>
       </c>
       <c r="E81" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="F81" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G81" s="1">
-        <v>45873</v>
+        <v>45239</v>
       </c>
       <c r="H81" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I81" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J81" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
       </c>
       <c r="C82">
-        <v>84</v>
+        <v>1043</v>
       </c>
       <c r="D82" t="s">
         <v>89</v>
       </c>
       <c r="E82" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="F82" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G82" s="1">
-        <v>45121</v>
+        <v>45680</v>
       </c>
       <c r="H82" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I82" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J82" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B83" t="s">
         <v>12</v>
       </c>
       <c r="C83">
-        <v>198</v>
+        <v>1017</v>
       </c>
       <c r="D83" t="s">
         <v>90</v>
       </c>
       <c r="E83" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F83" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G83" s="1">
-        <v>45936</v>
+        <v>45062</v>
       </c>
       <c r="H83" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I83" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J83" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B84" t="s">
         <v>12</v>
       </c>
       <c r="C84">
-        <v>133</v>
+        <v>1041</v>
       </c>
       <c r="D84" t="s">
         <v>91</v>
       </c>
       <c r="E84" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F84" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G84" s="1">
-        <v>45957</v>
+        <v>45689</v>
       </c>
       <c r="H84" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I84" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J84" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B85" t="s">
         <v>12</v>
       </c>
       <c r="C85">
-        <v>3</v>
+        <v>1027</v>
       </c>
       <c r="D85" t="s">
         <v>92</v>
       </c>
       <c r="E85" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F85" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G85" s="1">
-        <v>44348</v>
+        <v>45176</v>
       </c>
       <c r="H85" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I85" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J85" t="s">
-        <v>152</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" t="s">
+        <v>11</v>
+      </c>
+      <c r="B86" t="s">
+        <v>12</v>
+      </c>
+      <c r="C86">
+        <v>1013</v>
+      </c>
+      <c r="D86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E86" t="s">
+        <v>134</v>
+      </c>
+      <c r="F86" t="s">
+        <v>144</v>
+      </c>
+      <c r="G86" s="1">
+        <v>44929</v>
+      </c>
+      <c r="H86" t="s">
+        <v>145</v>
+      </c>
+      <c r="I86" t="s">
+        <v>148</v>
+      </c>
+      <c r="J86" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87">
+        <v>1008</v>
+      </c>
+      <c r="D87" t="s">
+        <v>94</v>
+      </c>
+      <c r="E87" t="s">
+        <v>136</v>
+      </c>
+      <c r="F87" t="s">
+        <v>144</v>
+      </c>
+      <c r="G87" s="1">
+        <v>46007</v>
+      </c>
+      <c r="H87" t="s">
+        <v>145</v>
+      </c>
+      <c r="I87" t="s">
+        <v>148</v>
+      </c>
+      <c r="J87" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/employees_CA.xlsx
+++ b/employees_CA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="162">
   <si>
     <t>Legal Name</t>
   </si>
@@ -61,12 +61,18 @@
     <t>Xinyi</t>
   </si>
   <si>
+    <t>David</t>
+  </si>
+  <si>
     <t>Hong</t>
   </si>
   <si>
     <t>Jian</t>
   </si>
   <si>
+    <t>Ye</t>
+  </si>
+  <si>
     <t>Zhenjun</t>
   </si>
   <si>
@@ -115,12 +121,12 @@
     <t>Enquan</t>
   </si>
   <si>
-    <t>Lixin</t>
-  </si>
-  <si>
     <t>Ting</t>
   </si>
   <si>
+    <t>Jiu</t>
+  </si>
+  <si>
     <t>KunIengCheong</t>
   </si>
   <si>
@@ -169,6 +175,9 @@
     <t>Boyu</t>
   </si>
   <si>
+    <t>Jose</t>
+  </si>
+  <si>
     <t>Zhiyi</t>
   </si>
   <si>
@@ -184,9 +193,15 @@
     <t>Jaime</t>
   </si>
   <si>
+    <t>Lanlan</t>
+  </si>
+  <si>
     <t>Yinghui</t>
   </si>
   <si>
+    <t>Zhaoyi</t>
+  </si>
+  <si>
     <t>Wingking</t>
   </si>
   <si>
@@ -199,16 +214,28 @@
     <t>CaiChin</t>
   </si>
   <si>
+    <t>German D</t>
+  </si>
+  <si>
     <t>Jiayu</t>
   </si>
   <si>
+    <t>Ying</t>
+  </si>
+  <si>
     <t>Weidong</t>
   </si>
   <si>
+    <t>Lexi</t>
+  </si>
+  <si>
     <t>Libang</t>
   </si>
   <si>
-    <t>Jiran</t>
+    <t>Yujian</t>
+  </si>
+  <si>
+    <t>Xiangju</t>
   </si>
   <si>
     <t>Ya-Han</t>
@@ -235,6 +262,9 @@
     <t>Yiyu</t>
   </si>
   <si>
+    <t>Yue</t>
+  </si>
+  <si>
     <t>Yuran</t>
   </si>
   <si>
@@ -271,36 +301,6 @@
     <t>Changqing</t>
   </si>
   <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>Ye</t>
-  </si>
-  <si>
-    <t>Jiu</t>
-  </si>
-  <si>
-    <t>Lanlan</t>
-  </si>
-  <si>
-    <t>Zhaoyi</t>
-  </si>
-  <si>
-    <t>Ying</t>
-  </si>
-  <si>
-    <t>Lexi</t>
-  </si>
-  <si>
-    <t>Yujian</t>
-  </si>
-  <si>
-    <t>Xiangju</t>
-  </si>
-  <si>
-    <t>Yue</t>
-  </si>
-  <si>
     <t>Bian</t>
   </si>
   <si>
@@ -376,6 +376,9 @@
     <t>Ma</t>
   </si>
   <si>
+    <t>Martinez</t>
+  </si>
+  <si>
     <t>Meng</t>
   </si>
   <si>
@@ -406,15 +409,24 @@
     <t>Tran</t>
   </si>
   <si>
+    <t>Vasquez Ortiz</t>
+  </si>
+  <si>
     <t>Wang</t>
   </si>
   <si>
     <t>Wei</t>
   </si>
   <si>
+    <t>Winstone</t>
+  </si>
+  <si>
     <t>Xia</t>
   </si>
   <si>
+    <t>Xiong</t>
+  </si>
+  <si>
     <t>Xu</t>
   </si>
   <si>
@@ -442,12 +454,6 @@
     <t>Zou</t>
   </si>
   <si>
-    <t>Winstone</t>
-  </si>
-  <si>
-    <t>Xiong</t>
-  </si>
-  <si>
     <t>Active</t>
   </si>
   <si>
@@ -469,6 +475,9 @@
     <t>Transfer - Transfer</t>
   </si>
   <si>
+    <t>Drop-Shipp - Drop-Shipping</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unloading - Unloading </t>
   </si>
   <si>
@@ -491,9 +500,6 @@
   </si>
   <si>
     <t>Commerce - Commerce Department</t>
-  </si>
-  <si>
-    <t>Drop-Shipp - Drop-Shipping</t>
   </si>
 </sst>
 </file>
@@ -881,19 +887,19 @@
         <v>95</v>
       </c>
       <c r="F2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G2" s="1">
         <v>45916</v>
       </c>
       <c r="H2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -913,30 +919,30 @@
         <v>96</v>
       </c>
       <c r="F3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G3" s="1">
         <v>46230</v>
       </c>
       <c r="H3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4">
-        <v>224</v>
+        <v>1012</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -945,19 +951,19 @@
         <v>97</v>
       </c>
       <c r="F4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G4" s="1">
-        <v>46168</v>
+        <v>44929</v>
       </c>
       <c r="H4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -968,7 +974,7 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>18</v>
+        <v>224</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
@@ -977,19 +983,19 @@
         <v>97</v>
       </c>
       <c r="F5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G5" s="1">
-        <v>43405</v>
+        <v>46168</v>
       </c>
       <c r="H5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1000,7 +1006,7 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1009,48 +1015,48 @@
         <v>97</v>
       </c>
       <c r="F6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G6" s="1">
-        <v>45909</v>
+        <v>43405</v>
       </c>
       <c r="H6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7">
-        <v>129</v>
+        <v>1040</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G7" s="1">
-        <v>45471</v>
+        <v>45684</v>
       </c>
       <c r="H7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J7" t="s">
         <v>153</v>
@@ -1064,28 +1070,28 @@
         <v>12</v>
       </c>
       <c r="C8">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G8" s="1">
-        <v>45701</v>
+        <v>45909</v>
       </c>
       <c r="H8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1096,28 +1102,28 @@
         <v>12</v>
       </c>
       <c r="C9">
-        <v>231</v>
+        <v>129</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G9" s="1">
-        <v>46225</v>
+        <v>45471</v>
       </c>
       <c r="H9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1128,28 +1134,28 @@
         <v>12</v>
       </c>
       <c r="C10">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G10" s="1">
-        <v>45538</v>
+        <v>45701</v>
       </c>
       <c r="H10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1160,28 +1166,28 @@
         <v>12</v>
       </c>
       <c r="C11">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="D11" t="s">
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G11" s="1">
-        <v>45915</v>
+        <v>46225</v>
       </c>
       <c r="H11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J11" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1192,28 +1198,28 @@
         <v>12</v>
       </c>
       <c r="C12">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s">
         <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G12" s="1">
-        <v>44317</v>
+        <v>45538</v>
       </c>
       <c r="H12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1224,28 +1230,28 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>119</v>
+        <v>193</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G13" s="1">
-        <v>45419</v>
+        <v>45915</v>
       </c>
       <c r="H13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1256,28 +1262,28 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
         <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F14" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G14" s="1">
-        <v>44069</v>
+        <v>44317</v>
       </c>
       <c r="H14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I14" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1288,28 +1294,28 @@
         <v>12</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F15" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G15" s="1">
-        <v>44756</v>
+        <v>45419</v>
       </c>
       <c r="H15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J15" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1320,28 +1326,28 @@
         <v>12</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D16" t="s">
         <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G16" s="1">
-        <v>44348</v>
+        <v>44069</v>
       </c>
       <c r="H16" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J16" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1352,28 +1358,28 @@
         <v>12</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G17" s="1">
-        <v>44452</v>
+        <v>44756</v>
       </c>
       <c r="H17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J17" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1384,25 +1390,25 @@
         <v>12</v>
       </c>
       <c r="C18">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="D18" t="s">
         <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F18" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G18" s="1">
-        <v>45536</v>
+        <v>44348</v>
       </c>
       <c r="H18" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I18" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J18" t="s">
         <v>154</v>
@@ -1416,28 +1422,28 @@
         <v>12</v>
       </c>
       <c r="C19">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="D19" t="s">
         <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F19" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G19" s="1">
-        <v>44774</v>
+        <v>44452</v>
       </c>
       <c r="H19" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J19" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1448,28 +1454,28 @@
         <v>12</v>
       </c>
       <c r="C20">
-        <v>225</v>
+        <v>160</v>
       </c>
       <c r="D20" t="s">
         <v>31</v>
       </c>
       <c r="E20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F20" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G20" s="1">
-        <v>46181</v>
+        <v>45536</v>
       </c>
       <c r="H20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J20" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1480,28 +1486,28 @@
         <v>12</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F21" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G21" s="1">
-        <v>43564</v>
+        <v>44774</v>
       </c>
       <c r="H21" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I21" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J21" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1512,28 +1518,28 @@
         <v>12</v>
       </c>
       <c r="C22">
-        <v>168</v>
+        <v>225</v>
       </c>
       <c r="D22" t="s">
         <v>33</v>
       </c>
       <c r="E22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F22" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G22" s="1">
-        <v>46090</v>
+        <v>46181</v>
       </c>
       <c r="H22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I22" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J22" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1544,28 +1550,28 @@
         <v>12</v>
       </c>
       <c r="C23">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F23" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G23" s="1">
-        <v>44508</v>
+        <v>43564</v>
       </c>
       <c r="H23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I23" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J23" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1576,60 +1582,60 @@
         <v>12</v>
       </c>
       <c r="C24">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D24" t="s">
         <v>35</v>
       </c>
       <c r="E24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F24" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G24" s="1">
-        <v>44774</v>
+        <v>44508</v>
       </c>
       <c r="H24" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J24" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
       </c>
       <c r="C25">
-        <v>190</v>
+        <v>1044</v>
       </c>
       <c r="D25" t="s">
         <v>36</v>
       </c>
       <c r="E25" t="s">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="F25" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G25" s="1">
-        <v>45902</v>
+        <v>45689</v>
       </c>
       <c r="H25" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I25" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J25" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1640,28 +1646,28 @@
         <v>12</v>
       </c>
       <c r="C26">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
         <v>37</v>
       </c>
       <c r="E26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F26" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G26" s="1">
-        <v>45047</v>
+        <v>44774</v>
       </c>
       <c r="H26" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I26" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J26" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1672,7 +1678,7 @@
         <v>12</v>
       </c>
       <c r="C27">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D27" t="s">
         <v>38</v>
@@ -1681,19 +1687,19 @@
         <v>112</v>
       </c>
       <c r="F27" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G27" s="1">
-        <v>45859</v>
+        <v>45902</v>
       </c>
       <c r="H27" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I27" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1704,7 +1710,7 @@
         <v>12</v>
       </c>
       <c r="C28">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
         <v>39</v>
@@ -1713,19 +1719,19 @@
         <v>112</v>
       </c>
       <c r="F28" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G28" s="1">
-        <v>45859</v>
+        <v>45047</v>
       </c>
       <c r="H28" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J28" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1736,28 +1742,28 @@
         <v>12</v>
       </c>
       <c r="C29">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D29" t="s">
         <v>40</v>
       </c>
       <c r="E29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F29" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G29" s="1">
-        <v>45809</v>
+        <v>45859</v>
       </c>
       <c r="H29" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I29" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J29" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1768,28 +1774,28 @@
         <v>12</v>
       </c>
       <c r="C30">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E30" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F30" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G30" s="1">
-        <v>46017</v>
+        <v>45859</v>
       </c>
       <c r="H30" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J30" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1800,28 +1806,28 @@
         <v>12</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>177</v>
       </c>
       <c r="D31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E31" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G31" s="1">
-        <v>45313</v>
+        <v>45809</v>
       </c>
       <c r="H31" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J31" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1832,28 +1838,28 @@
         <v>12</v>
       </c>
       <c r="C32">
-        <v>58</v>
+        <v>208</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G32" s="1">
-        <v>44858</v>
+        <v>46017</v>
       </c>
       <c r="H32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I32" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J32" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1864,7 +1870,7 @@
         <v>12</v>
       </c>
       <c r="C33">
-        <v>169</v>
+        <v>5</v>
       </c>
       <c r="D33" t="s">
         <v>43</v>
@@ -1873,19 +1879,19 @@
         <v>115</v>
       </c>
       <c r="F33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G33" s="1">
-        <v>45600</v>
+        <v>45313</v>
       </c>
       <c r="H33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1896,7 +1902,7 @@
         <v>12</v>
       </c>
       <c r="C34">
-        <v>207</v>
+        <v>58</v>
       </c>
       <c r="D34" t="s">
         <v>44</v>
@@ -1905,19 +1911,19 @@
         <v>115</v>
       </c>
       <c r="F34" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G34" s="1">
-        <v>46197</v>
+        <v>44858</v>
       </c>
       <c r="H34" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I34" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J34" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -1928,7 +1934,7 @@
         <v>12</v>
       </c>
       <c r="C35">
-        <v>217</v>
+        <v>169</v>
       </c>
       <c r="D35" t="s">
         <v>45</v>
@@ -1937,19 +1943,19 @@
         <v>115</v>
       </c>
       <c r="F35" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G35" s="1">
-        <v>46113</v>
+        <v>45600</v>
       </c>
       <c r="H35" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I35" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J35" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1960,7 +1966,7 @@
         <v>12</v>
       </c>
       <c r="C36">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D36" t="s">
         <v>46</v>
@@ -1969,19 +1975,19 @@
         <v>115</v>
       </c>
       <c r="F36" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G36" s="1">
-        <v>46070</v>
+        <v>46197</v>
       </c>
       <c r="H36" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I36" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J36" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1992,28 +1998,28 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D37" t="s">
         <v>47</v>
       </c>
       <c r="E37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F37" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G37" s="1">
-        <v>46181</v>
+        <v>46113</v>
       </c>
       <c r="H37" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I37" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J37" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2024,28 +2030,28 @@
         <v>12</v>
       </c>
       <c r="C38">
-        <v>48</v>
+        <v>212</v>
       </c>
       <c r="D38" t="s">
         <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G38" s="1">
-        <v>44348</v>
+        <v>46070</v>
       </c>
       <c r="H38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J38" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2056,28 +2062,28 @@
         <v>12</v>
       </c>
       <c r="C39">
-        <v>122</v>
+        <v>226</v>
       </c>
       <c r="D39" t="s">
         <v>49</v>
       </c>
       <c r="E39" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F39" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G39" s="1">
-        <v>46126</v>
+        <v>46181</v>
       </c>
       <c r="H39" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I39" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J39" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2088,28 +2094,28 @@
         <v>12</v>
       </c>
       <c r="C40">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D40" t="s">
         <v>50</v>
       </c>
       <c r="E40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F40" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G40" s="1">
-        <v>44802</v>
+        <v>44348</v>
       </c>
       <c r="H40" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I40" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2120,25 +2126,25 @@
         <v>12</v>
       </c>
       <c r="C41">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="D41" t="s">
         <v>51</v>
       </c>
       <c r="E41" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F41" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G41" s="1">
-        <v>45499</v>
+        <v>46126</v>
       </c>
       <c r="H41" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I41" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J41" t="s">
         <v>157</v>
@@ -2152,28 +2158,28 @@
         <v>12</v>
       </c>
       <c r="C42">
-        <v>200</v>
+        <v>46</v>
       </c>
       <c r="D42" t="s">
         <v>52</v>
       </c>
       <c r="E42" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F42" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G42" s="1">
-        <v>45957</v>
+        <v>44802</v>
       </c>
       <c r="H42" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I42" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J42" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2184,28 +2190,28 @@
         <v>12</v>
       </c>
       <c r="C43">
-        <v>15</v>
+        <v>234</v>
       </c>
       <c r="D43" t="s">
         <v>53</v>
       </c>
       <c r="E43" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F43" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G43" s="1">
-        <v>43922</v>
+        <v>46237</v>
       </c>
       <c r="H43" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I43" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2216,28 +2222,28 @@
         <v>12</v>
       </c>
       <c r="C44">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="D44" t="s">
         <v>54</v>
       </c>
       <c r="E44" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F44" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G44" s="1">
-        <v>45579</v>
+        <v>45499</v>
       </c>
       <c r="H44" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I44" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J44" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2248,28 +2254,28 @@
         <v>12</v>
       </c>
       <c r="C45">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="D45" t="s">
         <v>55</v>
       </c>
       <c r="E45" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F45" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G45" s="1">
-        <v>45509</v>
+        <v>45957</v>
       </c>
       <c r="H45" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I45" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J45" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2280,28 +2286,28 @@
         <v>12</v>
       </c>
       <c r="C46">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
         <v>56</v>
       </c>
       <c r="E46" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F46" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G46" s="1">
-        <v>46181</v>
+        <v>43922</v>
       </c>
       <c r="H46" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I46" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J46" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2312,28 +2318,28 @@
         <v>12</v>
       </c>
       <c r="C47">
-        <v>218</v>
+        <v>165</v>
       </c>
       <c r="D47" t="s">
         <v>57</v>
       </c>
       <c r="E47" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F47" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G47" s="1">
-        <v>46127</v>
+        <v>45579</v>
       </c>
       <c r="H47" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I47" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J47" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2344,60 +2350,60 @@
         <v>12</v>
       </c>
       <c r="C48">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="D48" t="s">
         <v>58</v>
       </c>
       <c r="E48" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F48" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G48" s="1">
-        <v>45778</v>
+        <v>45509</v>
       </c>
       <c r="H48" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I48" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J48" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
       </c>
       <c r="C49">
-        <v>41</v>
+        <v>1028</v>
       </c>
       <c r="D49" t="s">
         <v>59</v>
       </c>
       <c r="E49" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F49" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G49" s="1">
-        <v>44537</v>
+        <v>45239</v>
       </c>
       <c r="H49" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I49" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J49" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -2408,60 +2414,60 @@
         <v>12</v>
       </c>
       <c r="C50">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="D50" t="s">
         <v>60</v>
       </c>
       <c r="E50" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F50" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G50" s="1">
-        <v>45531</v>
+        <v>46181</v>
       </c>
       <c r="H50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J50" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
       </c>
       <c r="C51">
-        <v>170</v>
+        <v>1043</v>
       </c>
       <c r="D51" t="s">
         <v>61</v>
       </c>
       <c r="E51" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F51" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G51" s="1">
-        <v>45600</v>
+        <v>45680</v>
       </c>
       <c r="H51" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I51" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J51" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -2472,28 +2478,28 @@
         <v>12</v>
       </c>
       <c r="C52">
-        <v>166</v>
+        <v>218</v>
       </c>
       <c r="D52" t="s">
         <v>62</v>
       </c>
       <c r="E52" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F52" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G52" s="1">
-        <v>45586</v>
+        <v>46127</v>
       </c>
       <c r="H52" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I52" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J52" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -2504,28 +2510,28 @@
         <v>12</v>
       </c>
       <c r="C53">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="D53" t="s">
         <v>63</v>
       </c>
       <c r="E53" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F53" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G53" s="1">
-        <v>46048</v>
+        <v>45778</v>
       </c>
       <c r="H53" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I53" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J53" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -2536,28 +2542,28 @@
         <v>12</v>
       </c>
       <c r="C54">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D54" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E54" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F54" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G54" s="1">
-        <v>45243</v>
+        <v>44537</v>
       </c>
       <c r="H54" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I54" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J54" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -2568,28 +2574,28 @@
         <v>12</v>
       </c>
       <c r="C55">
-        <v>196</v>
+        <v>151</v>
       </c>
       <c r="D55" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E55" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F55" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G55" s="1">
-        <v>45924</v>
+        <v>45531</v>
       </c>
       <c r="H55" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I55" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J55" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -2600,28 +2606,28 @@
         <v>12</v>
       </c>
       <c r="C56">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="D56" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="E56" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F56" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G56" s="1">
-        <v>46141</v>
+        <v>46237</v>
       </c>
       <c r="H56" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I56" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J56" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -2632,60 +2638,60 @@
         <v>12</v>
       </c>
       <c r="C57">
-        <v>223</v>
+        <v>170</v>
       </c>
       <c r="D57" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E57" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F57" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G57" s="1">
-        <v>46163</v>
+        <v>45600</v>
       </c>
       <c r="H57" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I57" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J57" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
       </c>
       <c r="C58">
-        <v>121</v>
+        <v>1017</v>
       </c>
       <c r="D58" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E58" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F58" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G58" s="1">
-        <v>45432</v>
+        <v>45062</v>
       </c>
       <c r="H58" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I58" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J58" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -2696,60 +2702,60 @@
         <v>12</v>
       </c>
       <c r="C59">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="D59" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E59" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="F59" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G59" s="1">
-        <v>46062</v>
+        <v>45586</v>
       </c>
       <c r="H59" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I59" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J59" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B60" t="s">
         <v>12</v>
       </c>
       <c r="C60">
-        <v>65</v>
+        <v>1041</v>
       </c>
       <c r="D60" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F60" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G60" s="1">
-        <v>44909</v>
+        <v>45689</v>
       </c>
       <c r="H60" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I60" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -2760,60 +2766,60 @@
         <v>12</v>
       </c>
       <c r="C61">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D61" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E61" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F61" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G61" s="1">
-        <v>45978</v>
+        <v>46048</v>
       </c>
       <c r="H61" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I61" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J61" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
       </c>
       <c r="C62">
-        <v>199</v>
+        <v>1027</v>
       </c>
       <c r="D62" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E62" t="s">
         <v>136</v>
       </c>
       <c r="F62" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G62" s="1">
-        <v>45938</v>
+        <v>45176</v>
       </c>
       <c r="H62" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I62" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J62" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -2824,28 +2830,28 @@
         <v>12</v>
       </c>
       <c r="C63">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="D63" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E63" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F63" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G63" s="1">
-        <v>46146</v>
+        <v>45243</v>
       </c>
       <c r="H63" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I63" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J63" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -2856,60 +2862,60 @@
         <v>12</v>
       </c>
       <c r="C64">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D64" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="E64" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F64" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G64" s="1">
-        <v>46076</v>
+        <v>46141</v>
       </c>
       <c r="H64" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I64" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J64" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B65" t="s">
         <v>12</v>
       </c>
       <c r="C65">
-        <v>127</v>
+        <v>1013</v>
       </c>
       <c r="D65" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E65" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F65" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G65" s="1">
-        <v>45444</v>
+        <v>44929</v>
       </c>
       <c r="H65" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I65" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J65" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -2920,28 +2926,28 @@
         <v>12</v>
       </c>
       <c r="C66">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="D66" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E66" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F66" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G66" s="1">
-        <v>46076</v>
+        <v>46163</v>
       </c>
       <c r="H66" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I66" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J66" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -2952,28 +2958,28 @@
         <v>12</v>
       </c>
       <c r="C67">
-        <v>229</v>
+        <v>121</v>
       </c>
       <c r="D67" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E67" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F67" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G67" s="1">
-        <v>46197</v>
+        <v>45432</v>
       </c>
       <c r="H67" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I67" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J67" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -2984,28 +2990,28 @@
         <v>12</v>
       </c>
       <c r="C68">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D68" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E68" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="F68" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G68" s="1">
-        <v>45894</v>
+        <v>46062</v>
       </c>
       <c r="H68" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I68" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J68" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -3016,28 +3022,28 @@
         <v>12</v>
       </c>
       <c r="C69">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="D69" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E69" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F69" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G69" s="1">
-        <v>44287</v>
+        <v>44909</v>
       </c>
       <c r="H69" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I69" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J69" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -3048,28 +3054,28 @@
         <v>12</v>
       </c>
       <c r="C70">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D70" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E70" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F70" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G70" s="1">
         <v>45978</v>
       </c>
       <c r="H70" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I70" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J70" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -3080,28 +3086,28 @@
         <v>12</v>
       </c>
       <c r="C71">
-        <v>22</v>
+        <v>199</v>
       </c>
       <c r="D71" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E71" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F71" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G71" s="1">
-        <v>44683</v>
+        <v>45938</v>
       </c>
       <c r="H71" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I71" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J71" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3112,28 +3118,28 @@
         <v>12</v>
       </c>
       <c r="C72">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D72" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="E72" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F72" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G72" s="1">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="H72" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I72" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J72" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -3144,28 +3150,28 @@
         <v>12</v>
       </c>
       <c r="C73">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="D73" t="s">
         <v>80</v>
       </c>
       <c r="E73" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F73" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G73" s="1">
-        <v>45873</v>
+        <v>46076</v>
       </c>
       <c r="H73" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I73" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J73" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3176,60 +3182,60 @@
         <v>12</v>
       </c>
       <c r="C74">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="D74" t="s">
         <v>81</v>
       </c>
       <c r="E74" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F74" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G74" s="1">
-        <v>45121</v>
+        <v>45444</v>
       </c>
       <c r="H74" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I74" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J74" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
       </c>
       <c r="C75">
-        <v>198</v>
+        <v>1008</v>
       </c>
       <c r="D75" t="s">
         <v>82</v>
       </c>
       <c r="E75" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F75" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G75" s="1">
-        <v>45936</v>
+        <v>46007</v>
       </c>
       <c r="H75" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I75" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J75" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3240,7 +3246,7 @@
         <v>12</v>
       </c>
       <c r="C76">
-        <v>133</v>
+        <v>214</v>
       </c>
       <c r="D76" t="s">
         <v>83</v>
@@ -3249,19 +3255,19 @@
         <v>140</v>
       </c>
       <c r="F76" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G76" s="1">
-        <v>45957</v>
+        <v>46076</v>
       </c>
       <c r="H76" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I76" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J76" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3272,7 +3278,7 @@
         <v>12</v>
       </c>
       <c r="C77">
-        <v>3</v>
+        <v>229</v>
       </c>
       <c r="D77" t="s">
         <v>84</v>
@@ -3281,48 +3287,48 @@
         <v>141</v>
       </c>
       <c r="F77" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G77" s="1">
-        <v>44348</v>
+        <v>46197</v>
       </c>
       <c r="H77" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I77" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J77" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B78" t="s">
         <v>12</v>
       </c>
       <c r="C78">
-        <v>1012</v>
+        <v>189</v>
       </c>
       <c r="D78" t="s">
         <v>85</v>
       </c>
       <c r="E78" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="F78" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G78" s="1">
-        <v>44929</v>
+        <v>45894</v>
       </c>
       <c r="H78" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I78" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J78" t="s">
         <v>159</v>
@@ -3330,95 +3336,95 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
       </c>
       <c r="C79">
-        <v>1040</v>
+        <v>9</v>
       </c>
       <c r="D79" t="s">
         <v>86</v>
       </c>
       <c r="E79" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="F79" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G79" s="1">
-        <v>45684</v>
+        <v>44287</v>
       </c>
       <c r="H79" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I79" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J79" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B80" t="s">
         <v>12</v>
       </c>
       <c r="C80">
-        <v>1044</v>
+        <v>204</v>
       </c>
       <c r="D80" t="s">
         <v>87</v>
       </c>
       <c r="E80" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="F80" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G80" s="1">
-        <v>45689</v>
+        <v>45978</v>
       </c>
       <c r="H80" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I80" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J80" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B81" t="s">
         <v>12</v>
       </c>
       <c r="C81">
-        <v>1028</v>
+        <v>22</v>
       </c>
       <c r="D81" t="s">
         <v>88</v>
       </c>
       <c r="E81" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="F81" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G81" s="1">
-        <v>45239</v>
+        <v>44683</v>
       </c>
       <c r="H81" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I81" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J81" t="s">
         <v>159</v>
@@ -3426,109 +3432,109 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
       </c>
       <c r="C82">
-        <v>1043</v>
+        <v>228</v>
       </c>
       <c r="D82" t="s">
         <v>89</v>
       </c>
       <c r="E82" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="F82" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G82" s="1">
-        <v>45680</v>
+        <v>46153</v>
       </c>
       <c r="H82" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I82" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J82" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B83" t="s">
         <v>12</v>
       </c>
       <c r="C83">
-        <v>1017</v>
+        <v>187</v>
       </c>
       <c r="D83" t="s">
         <v>90</v>
       </c>
       <c r="E83" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F83" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G83" s="1">
-        <v>45062</v>
+        <v>45873</v>
       </c>
       <c r="H83" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I83" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J83" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B84" t="s">
         <v>12</v>
       </c>
       <c r="C84">
-        <v>1041</v>
+        <v>84</v>
       </c>
       <c r="D84" t="s">
         <v>91</v>
       </c>
       <c r="E84" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F84" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G84" s="1">
-        <v>45689</v>
+        <v>45121</v>
       </c>
       <c r="H84" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I84" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J84" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B85" t="s">
         <v>12</v>
       </c>
       <c r="C85">
-        <v>1027</v>
+        <v>198</v>
       </c>
       <c r="D85" t="s">
         <v>92</v>
@@ -3537,16 +3543,16 @@
         <v>143</v>
       </c>
       <c r="F85" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G85" s="1">
-        <v>45176</v>
+        <v>45936</v>
       </c>
       <c r="H85" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I85" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J85" t="s">
         <v>159</v>
@@ -3554,66 +3560,66 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
       </c>
       <c r="C86">
-        <v>1013</v>
+        <v>133</v>
       </c>
       <c r="D86" t="s">
         <v>93</v>
       </c>
       <c r="E86" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F86" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G86" s="1">
-        <v>44929</v>
+        <v>45957</v>
       </c>
       <c r="H86" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I86" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J86" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B87" t="s">
         <v>12</v>
       </c>
       <c r="C87">
-        <v>1008</v>
+        <v>3</v>
       </c>
       <c r="D87" t="s">
         <v>94</v>
       </c>
       <c r="E87" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="F87" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G87" s="1">
-        <v>46007</v>
+        <v>44348</v>
       </c>
       <c r="H87" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I87" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J87" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/employees_CA.xlsx
+++ b/employees_CA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="166">
   <si>
     <t>Legal Name</t>
   </si>
@@ -73,6 +73,9 @@
     <t>Ye</t>
   </si>
   <si>
+    <t>Yixiong</t>
+  </si>
+  <si>
     <t>Zhenjun</t>
   </si>
   <si>
@@ -103,6 +106,9 @@
     <t>Aixin</t>
   </si>
   <si>
+    <t>Zhengjie</t>
+  </si>
+  <si>
     <t>Bin</t>
   </si>
   <si>
@@ -163,6 +169,9 @@
     <t>Yinli</t>
   </si>
   <si>
+    <t>Zhilong</t>
+  </si>
+  <si>
     <t>Arze</t>
   </si>
   <si>
@@ -193,6 +202,9 @@
     <t>Jaime</t>
   </si>
   <si>
+    <t>Yanting</t>
+  </si>
+  <si>
     <t>Lanlan</t>
   </si>
   <si>
@@ -211,15 +223,9 @@
     <t>Yi</t>
   </si>
   <si>
-    <t>CaiChin</t>
-  </si>
-  <si>
     <t>German D</t>
   </si>
   <si>
-    <t>Jiayu</t>
-  </si>
-  <si>
     <t>Ying</t>
   </si>
   <si>
@@ -244,9 +250,6 @@
     <t>Zhen</t>
   </si>
   <si>
-    <t>Xinyuan</t>
-  </si>
-  <si>
     <t>Guang</t>
   </si>
   <si>
@@ -268,9 +271,6 @@
     <t>Yuran</t>
   </si>
   <si>
-    <t>Huan</t>
-  </si>
-  <si>
     <t>Qianyang</t>
   </si>
   <si>
@@ -334,6 +334,9 @@
     <t>Gu</t>
   </si>
   <si>
+    <t>Guan</t>
+  </si>
+  <si>
     <t>Guo</t>
   </si>
   <si>
@@ -394,6 +397,9 @@
     <t>Rodriguez</t>
   </si>
   <si>
+    <t>Song</t>
+  </si>
+  <si>
     <t>Sun</t>
   </si>
   <si>
@@ -406,9 +412,6 @@
     <t>Tian</t>
   </si>
   <si>
-    <t>Tran</t>
-  </si>
-  <si>
     <t>Vasquez Ortiz</t>
   </si>
   <si>
@@ -472,13 +475,13 @@
     <t>Executive - Executive</t>
   </si>
   <si>
-    <t>Transfer - Transfer</t>
+    <t>Inventory - Department Inventory</t>
   </si>
   <si>
     <t>Drop-Shipp - Drop-Shipping</t>
   </si>
   <si>
-    <t xml:space="preserve">Unloading - Unloading </t>
+    <t>Outbound - Department Outbound</t>
   </si>
   <si>
     <t>HR - HR</t>
@@ -487,19 +490,28 @@
     <t>QC - QC</t>
   </si>
   <si>
-    <t>Shipping - Shipping</t>
-  </si>
-  <si>
-    <t>Accounting - Accounting</t>
+    <t>Finance - Department Finance</t>
   </si>
   <si>
     <t>Dispatch - Dispatching Center</t>
   </si>
   <si>
+    <t>CS - Department CS</t>
+  </si>
+  <si>
+    <t>Inbound - Department Inbound</t>
+  </si>
+  <si>
+    <t>Receiving - Receiving</t>
+  </si>
+  <si>
+    <t>MS - Department MS</t>
+  </si>
+  <si>
     <t>Resource - Resource Center</t>
   </si>
   <si>
-    <t>Commerce - Commerce Department</t>
+    <t>Product - Department Product</t>
   </si>
 </sst>
 </file>
@@ -887,19 +899,19 @@
         <v>95</v>
       </c>
       <c r="F2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G2" s="1">
         <v>45916</v>
       </c>
       <c r="H2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -919,19 +931,19 @@
         <v>96</v>
       </c>
       <c r="F3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G3" s="1">
         <v>46230</v>
       </c>
       <c r="H3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -951,19 +963,19 @@
         <v>97</v>
       </c>
       <c r="F4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G4" s="1">
         <v>44929</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -983,19 +995,19 @@
         <v>97</v>
       </c>
       <c r="F5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G5" s="1">
         <v>46168</v>
       </c>
       <c r="H5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1015,19 +1027,19 @@
         <v>97</v>
       </c>
       <c r="F6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G6" s="1">
         <v>43405</v>
       </c>
       <c r="H6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1047,19 +1059,19 @@
         <v>97</v>
       </c>
       <c r="F7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G7" s="1">
         <v>45684</v>
       </c>
       <c r="H7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1070,7 +1082,7 @@
         <v>12</v>
       </c>
       <c r="C8">
-        <v>191</v>
+        <v>236</v>
       </c>
       <c r="D8" t="s">
         <v>19</v>
@@ -1079,13 +1091,13 @@
         <v>97</v>
       </c>
       <c r="F8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G8" s="1">
-        <v>45909</v>
+        <v>46223</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I8" t="s">
         <v>150</v>
@@ -1102,28 +1114,28 @@
         <v>12</v>
       </c>
       <c r="C9">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G9" s="1">
-        <v>45471</v>
+        <v>45909</v>
       </c>
       <c r="H9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1134,28 +1146,28 @@
         <v>12</v>
       </c>
       <c r="C10">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G10" s="1">
-        <v>45701</v>
+        <v>45471</v>
       </c>
       <c r="H10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I10" t="s">
         <v>150</v>
       </c>
       <c r="J10" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1166,28 +1178,28 @@
         <v>12</v>
       </c>
       <c r="C11">
-        <v>231</v>
+        <v>174</v>
       </c>
       <c r="D11" t="s">
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G11" s="1">
-        <v>46225</v>
+        <v>45701</v>
       </c>
       <c r="H11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J11" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1198,28 +1210,28 @@
         <v>12</v>
       </c>
       <c r="C12">
-        <v>154</v>
+        <v>231</v>
       </c>
       <c r="D12" t="s">
         <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G12" s="1">
-        <v>45538</v>
+        <v>46225</v>
       </c>
       <c r="H12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J12" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1230,28 +1242,28 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G13" s="1">
-        <v>45915</v>
+        <v>45538</v>
       </c>
       <c r="H13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1262,7 +1274,7 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>40</v>
+        <v>193</v>
       </c>
       <c r="D14" t="s">
         <v>25</v>
@@ -1271,19 +1283,19 @@
         <v>102</v>
       </c>
       <c r="F14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G14" s="1">
-        <v>44317</v>
+        <v>45915</v>
       </c>
       <c r="H14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J14" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1294,28 +1306,28 @@
         <v>12</v>
       </c>
       <c r="C15">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G15" s="1">
-        <v>45419</v>
+        <v>44317</v>
       </c>
       <c r="H15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I15" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1326,28 +1338,28 @@
         <v>12</v>
       </c>
       <c r="C16">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="D16" t="s">
         <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G16" s="1">
-        <v>44069</v>
+        <v>45419</v>
       </c>
       <c r="H16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J16" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1358,28 +1370,28 @@
         <v>12</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G17" s="1">
-        <v>44756</v>
+        <v>44069</v>
       </c>
       <c r="H17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1390,28 +1402,28 @@
         <v>12</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="s">
         <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G18" s="1">
-        <v>44348</v>
+        <v>44756</v>
       </c>
       <c r="H18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I18" t="s">
         <v>150</v>
       </c>
       <c r="J18" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1422,7 +1434,7 @@
         <v>12</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>237</v>
       </c>
       <c r="D19" t="s">
         <v>30</v>
@@ -1431,19 +1443,19 @@
         <v>106</v>
       </c>
       <c r="F19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G19" s="1">
-        <v>44452</v>
+        <v>46252</v>
       </c>
       <c r="H19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J19" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1454,7 +1466,7 @@
         <v>12</v>
       </c>
       <c r="C20">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="D20" t="s">
         <v>31</v>
@@ -1463,19 +1475,19 @@
         <v>107</v>
       </c>
       <c r="F20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G20" s="1">
-        <v>45536</v>
+        <v>44348</v>
       </c>
       <c r="H20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J20" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1486,7 +1498,7 @@
         <v>12</v>
       </c>
       <c r="C21">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
@@ -1495,19 +1507,19 @@
         <v>107</v>
       </c>
       <c r="F21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G21" s="1">
-        <v>44774</v>
+        <v>44452</v>
       </c>
       <c r="H21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J21" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1518,7 +1530,7 @@
         <v>12</v>
       </c>
       <c r="C22">
-        <v>225</v>
+        <v>160</v>
       </c>
       <c r="D22" t="s">
         <v>33</v>
@@ -1527,19 +1539,19 @@
         <v>108</v>
       </c>
       <c r="F22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G22" s="1">
-        <v>46181</v>
+        <v>45536</v>
       </c>
       <c r="H22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I22" t="s">
         <v>150</v>
       </c>
       <c r="J22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1550,28 +1562,28 @@
         <v>12</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G23" s="1">
-        <v>43564</v>
+        <v>44774</v>
       </c>
       <c r="H23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J23" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1582,60 +1594,60 @@
         <v>12</v>
       </c>
       <c r="C24">
-        <v>56</v>
+        <v>225</v>
       </c>
       <c r="D24" t="s">
         <v>35</v>
       </c>
       <c r="E24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G24" s="1">
-        <v>44508</v>
+        <v>46181</v>
       </c>
       <c r="H24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I24" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J24" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
       </c>
       <c r="C25">
-        <v>1044</v>
+        <v>7</v>
       </c>
       <c r="D25" t="s">
         <v>36</v>
       </c>
       <c r="E25" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="F25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G25" s="1">
-        <v>45689</v>
+        <v>43564</v>
       </c>
       <c r="H25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I25" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J25" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1646,7 +1658,7 @@
         <v>12</v>
       </c>
       <c r="C26">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D26" t="s">
         <v>37</v>
@@ -1655,51 +1667,51 @@
         <v>111</v>
       </c>
       <c r="F26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G26" s="1">
-        <v>44774</v>
+        <v>44508</v>
       </c>
       <c r="H26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I26" t="s">
         <v>150</v>
       </c>
       <c r="J26" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
       </c>
       <c r="C27">
-        <v>190</v>
+        <v>1044</v>
       </c>
       <c r="D27" t="s">
         <v>38</v>
       </c>
       <c r="E27" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G27" s="1">
-        <v>45902</v>
+        <v>45689</v>
       </c>
       <c r="H27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I27" t="s">
         <v>150</v>
       </c>
       <c r="J27" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1710,7 +1722,7 @@
         <v>12</v>
       </c>
       <c r="C28">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D28" t="s">
         <v>39</v>
@@ -1719,19 +1731,19 @@
         <v>112</v>
       </c>
       <c r="F28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G28" s="1">
-        <v>45047</v>
+        <v>44774</v>
       </c>
       <c r="H28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I28" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J28" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1742,28 +1754,28 @@
         <v>12</v>
       </c>
       <c r="C29">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D29" t="s">
         <v>40</v>
       </c>
       <c r="E29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G29" s="1">
-        <v>45859</v>
+        <v>45902</v>
       </c>
       <c r="H29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1774,28 +1786,28 @@
         <v>12</v>
       </c>
       <c r="C30">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
         <v>41</v>
       </c>
       <c r="E30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G30" s="1">
-        <v>45859</v>
+        <v>45047</v>
       </c>
       <c r="H30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I30" t="s">
         <v>150</v>
       </c>
       <c r="J30" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1806,7 +1818,7 @@
         <v>12</v>
       </c>
       <c r="C31">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D31" t="s">
         <v>42</v>
@@ -1815,19 +1827,19 @@
         <v>113</v>
       </c>
       <c r="F31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G31" s="1">
-        <v>45809</v>
+        <v>45859</v>
       </c>
       <c r="H31" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I31" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J31" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1838,28 +1850,28 @@
         <v>12</v>
       </c>
       <c r="C32">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F32" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G32" s="1">
-        <v>46017</v>
+        <v>45859</v>
       </c>
       <c r="H32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I32" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J32" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1870,28 +1882,28 @@
         <v>12</v>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>177</v>
       </c>
       <c r="D33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G33" s="1">
-        <v>45313</v>
+        <v>45809</v>
       </c>
       <c r="H33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I33" t="s">
         <v>150</v>
       </c>
       <c r="J33" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1902,28 +1914,28 @@
         <v>12</v>
       </c>
       <c r="C34">
-        <v>58</v>
+        <v>208</v>
       </c>
       <c r="D34" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E34" t="s">
         <v>115</v>
       </c>
       <c r="F34" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G34" s="1">
-        <v>44858</v>
+        <v>46017</v>
       </c>
       <c r="H34" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I34" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J34" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -1934,28 +1946,28 @@
         <v>12</v>
       </c>
       <c r="C35">
-        <v>169</v>
+        <v>5</v>
       </c>
       <c r="D35" t="s">
         <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G35" s="1">
-        <v>45600</v>
+        <v>45313</v>
       </c>
       <c r="H35" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J35" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1966,28 +1978,28 @@
         <v>12</v>
       </c>
       <c r="C36">
-        <v>207</v>
+        <v>58</v>
       </c>
       <c r="D36" t="s">
         <v>46</v>
       </c>
       <c r="E36" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F36" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G36" s="1">
-        <v>46197</v>
+        <v>44858</v>
       </c>
       <c r="H36" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I36" t="s">
         <v>150</v>
       </c>
       <c r="J36" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1998,28 +2010,28 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>217</v>
+        <v>169</v>
       </c>
       <c r="D37" t="s">
         <v>47</v>
       </c>
       <c r="E37" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F37" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G37" s="1">
-        <v>46113</v>
+        <v>45600</v>
       </c>
       <c r="H37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I37" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J37" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2030,28 +2042,28 @@
         <v>12</v>
       </c>
       <c r="C38">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D38" t="s">
         <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F38" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G38" s="1">
-        <v>46070</v>
+        <v>46197</v>
       </c>
       <c r="H38" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I38" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2062,7 +2074,7 @@
         <v>12</v>
       </c>
       <c r="C39">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D39" t="s">
         <v>49</v>
@@ -2071,19 +2083,19 @@
         <v>116</v>
       </c>
       <c r="F39" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G39" s="1">
-        <v>46181</v>
+        <v>46113</v>
       </c>
       <c r="H39" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" t="s">
         <v>150</v>
       </c>
       <c r="J39" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2094,28 +2106,28 @@
         <v>12</v>
       </c>
       <c r="C40">
-        <v>48</v>
+        <v>212</v>
       </c>
       <c r="D40" t="s">
         <v>50</v>
       </c>
       <c r="E40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G40" s="1">
-        <v>44348</v>
+        <v>46070</v>
       </c>
       <c r="H40" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I40" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J40" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2126,28 +2138,28 @@
         <v>12</v>
       </c>
       <c r="C41">
-        <v>122</v>
+        <v>238</v>
       </c>
       <c r="D41" t="s">
         <v>51</v>
       </c>
       <c r="E41" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G41" s="1">
-        <v>46126</v>
+        <v>46254</v>
       </c>
       <c r="H41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I41" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J41" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2158,28 +2170,28 @@
         <v>12</v>
       </c>
       <c r="C42">
-        <v>46</v>
+        <v>226</v>
       </c>
       <c r="D42" t="s">
         <v>52</v>
       </c>
       <c r="E42" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F42" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G42" s="1">
-        <v>44802</v>
+        <v>46181</v>
       </c>
       <c r="H42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J42" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2190,28 +2202,28 @@
         <v>12</v>
       </c>
       <c r="C43">
-        <v>234</v>
+        <v>48</v>
       </c>
       <c r="D43" t="s">
         <v>53</v>
       </c>
       <c r="E43" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G43" s="1">
-        <v>46237</v>
+        <v>44348</v>
       </c>
       <c r="H43" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I43" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J43" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2222,28 +2234,28 @@
         <v>12</v>
       </c>
       <c r="C44">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="D44" t="s">
         <v>54</v>
       </c>
       <c r="E44" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F44" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G44" s="1">
-        <v>45499</v>
+        <v>46126</v>
       </c>
       <c r="H44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I44" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J44" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2254,28 +2266,28 @@
         <v>12</v>
       </c>
       <c r="C45">
-        <v>200</v>
+        <v>46</v>
       </c>
       <c r="D45" t="s">
         <v>55</v>
       </c>
       <c r="E45" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F45" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G45" s="1">
-        <v>45957</v>
+        <v>44802</v>
       </c>
       <c r="H45" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J45" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2286,28 +2298,28 @@
         <v>12</v>
       </c>
       <c r="C46">
-        <v>15</v>
+        <v>234</v>
       </c>
       <c r="D46" t="s">
         <v>56</v>
       </c>
       <c r="E46" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F46" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G46" s="1">
-        <v>43922</v>
+        <v>46237</v>
       </c>
       <c r="H46" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I46" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J46" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2318,28 +2330,28 @@
         <v>12</v>
       </c>
       <c r="C47">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="D47" t="s">
         <v>57</v>
       </c>
       <c r="E47" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F47" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G47" s="1">
-        <v>45579</v>
+        <v>45499</v>
       </c>
       <c r="H47" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J47" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2350,60 +2362,60 @@
         <v>12</v>
       </c>
       <c r="C48">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="D48" t="s">
         <v>58</v>
       </c>
       <c r="E48" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F48" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G48" s="1">
-        <v>45509</v>
+        <v>45957</v>
       </c>
       <c r="H48" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I48" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J48" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
       </c>
       <c r="C49">
-        <v>1028</v>
+        <v>15</v>
       </c>
       <c r="D49" t="s">
         <v>59</v>
       </c>
       <c r="E49" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G49" s="1">
-        <v>45239</v>
+        <v>43922</v>
       </c>
       <c r="H49" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I49" t="s">
         <v>150</v>
       </c>
       <c r="J49" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -2414,39 +2426,39 @@
         <v>12</v>
       </c>
       <c r="C50">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="D50" t="s">
         <v>60</v>
       </c>
       <c r="E50" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G50" s="1">
-        <v>46181</v>
+        <v>45579</v>
       </c>
       <c r="H50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I50" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J50" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
       </c>
       <c r="C51">
-        <v>1043</v>
+        <v>147</v>
       </c>
       <c r="D51" t="s">
         <v>61</v>
@@ -2455,19 +2467,19 @@
         <v>126</v>
       </c>
       <c r="F51" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G51" s="1">
-        <v>45680</v>
+        <v>45509</v>
       </c>
       <c r="H51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I51" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J51" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -2478,7 +2490,7 @@
         <v>12</v>
       </c>
       <c r="C52">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="D52" t="s">
         <v>62</v>
@@ -2487,30 +2499,30 @@
         <v>127</v>
       </c>
       <c r="F52" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G52" s="1">
-        <v>46127</v>
+        <v>46244</v>
       </c>
       <c r="H52" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I52" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J52" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
       </c>
       <c r="C53">
-        <v>176</v>
+        <v>1028</v>
       </c>
       <c r="D53" t="s">
         <v>63</v>
@@ -2519,19 +2531,19 @@
         <v>128</v>
       </c>
       <c r="F53" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G53" s="1">
-        <v>45778</v>
+        <v>45239</v>
       </c>
       <c r="H53" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I53" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J53" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -2542,60 +2554,60 @@
         <v>12</v>
       </c>
       <c r="C54">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="D54" t="s">
         <v>64</v>
       </c>
       <c r="E54" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F54" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G54" s="1">
-        <v>44537</v>
+        <v>46181</v>
       </c>
       <c r="H54" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I54" t="s">
         <v>150</v>
       </c>
       <c r="J54" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
       </c>
       <c r="C55">
-        <v>151</v>
+        <v>1043</v>
       </c>
       <c r="D55" t="s">
         <v>65</v>
       </c>
       <c r="E55" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G55" s="1">
-        <v>45531</v>
+        <v>45680</v>
       </c>
       <c r="H55" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I55" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J55" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -2606,28 +2618,28 @@
         <v>12</v>
       </c>
       <c r="C56">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="D56" t="s">
         <v>66</v>
       </c>
       <c r="E56" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F56" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G56" s="1">
-        <v>46237</v>
+        <v>46127</v>
       </c>
       <c r="H56" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I56" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J56" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -2638,60 +2650,60 @@
         <v>12</v>
       </c>
       <c r="C57">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D57" t="s">
         <v>67</v>
       </c>
       <c r="E57" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F57" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G57" s="1">
-        <v>45600</v>
+        <v>45778</v>
       </c>
       <c r="H57" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I57" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
       </c>
       <c r="C58">
-        <v>1017</v>
+        <v>41</v>
       </c>
       <c r="D58" t="s">
         <v>68</v>
       </c>
       <c r="E58" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F58" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G58" s="1">
-        <v>45062</v>
+        <v>44537</v>
       </c>
       <c r="H58" t="s">
         <v>148</v>
       </c>
       <c r="I58" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J58" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -2702,28 +2714,28 @@
         <v>12</v>
       </c>
       <c r="C59">
-        <v>166</v>
+        <v>233</v>
       </c>
       <c r="D59" t="s">
         <v>69</v>
       </c>
       <c r="E59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F59" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G59" s="1">
-        <v>45586</v>
+        <v>46237</v>
       </c>
       <c r="H59" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J59" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -2734,28 +2746,28 @@
         <v>12</v>
       </c>
       <c r="C60">
-        <v>1041</v>
+        <v>1017</v>
       </c>
       <c r="D60" t="s">
         <v>70</v>
       </c>
       <c r="E60" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F60" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G60" s="1">
-        <v>45689</v>
+        <v>45062</v>
       </c>
       <c r="H60" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I60" t="s">
         <v>150</v>
       </c>
       <c r="J60" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -2766,28 +2778,28 @@
         <v>12</v>
       </c>
       <c r="C61">
-        <v>209</v>
+        <v>166</v>
       </c>
       <c r="D61" t="s">
         <v>71</v>
       </c>
       <c r="E61" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F61" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G61" s="1">
-        <v>46048</v>
+        <v>45586</v>
       </c>
       <c r="H61" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I61" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J61" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -2798,28 +2810,28 @@
         <v>12</v>
       </c>
       <c r="C62">
-        <v>1027</v>
+        <v>1041</v>
       </c>
       <c r="D62" t="s">
         <v>72</v>
       </c>
       <c r="E62" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F62" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G62" s="1">
-        <v>45176</v>
+        <v>45689</v>
       </c>
       <c r="H62" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I62" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J62" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -2830,89 +2842,89 @@
         <v>12</v>
       </c>
       <c r="C63">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="D63" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="E63" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F63" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G63" s="1">
-        <v>45243</v>
+        <v>46048</v>
       </c>
       <c r="H63" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I63" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J63" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
       </c>
       <c r="C64">
-        <v>220</v>
+        <v>1027</v>
       </c>
       <c r="D64" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="E64" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F64" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G64" s="1">
-        <v>46141</v>
+        <v>45176</v>
       </c>
       <c r="H64" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I64" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J64" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B65" t="s">
         <v>12</v>
       </c>
       <c r="C65">
-        <v>1013</v>
+        <v>21</v>
       </c>
       <c r="D65" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="E65" t="s">
         <v>138</v>
       </c>
       <c r="F65" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G65" s="1">
-        <v>44929</v>
+        <v>45243</v>
       </c>
       <c r="H65" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I65" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J65" t="s">
         <v>153</v>
@@ -2926,60 +2938,60 @@
         <v>12</v>
       </c>
       <c r="C66">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D66" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="E66" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F66" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G66" s="1">
-        <v>46163</v>
+        <v>46141</v>
       </c>
       <c r="H66" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I66" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J66" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
       </c>
       <c r="C67">
-        <v>121</v>
+        <v>1013</v>
       </c>
       <c r="D67" t="s">
         <v>75</v>
       </c>
       <c r="E67" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F67" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G67" s="1">
-        <v>45432</v>
+        <v>44929</v>
       </c>
       <c r="H67" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I67" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J67" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -2990,28 +3002,28 @@
         <v>12</v>
       </c>
       <c r="C68">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D68" t="s">
         <v>76</v>
       </c>
       <c r="E68" t="s">
-        <v>64</v>
+        <v>139</v>
       </c>
       <c r="F68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G68" s="1">
-        <v>46062</v>
+        <v>46163</v>
       </c>
       <c r="H68" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I68" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J68" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -3022,7 +3034,7 @@
         <v>12</v>
       </c>
       <c r="C69">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="D69" t="s">
         <v>77</v>
@@ -3031,19 +3043,19 @@
         <v>139</v>
       </c>
       <c r="F69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G69" s="1">
-        <v>44909</v>
+        <v>45432</v>
       </c>
       <c r="H69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I69" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J69" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -3054,7 +3066,7 @@
         <v>12</v>
       </c>
       <c r="C70">
-        <v>205</v>
+        <v>65</v>
       </c>
       <c r="D70" t="s">
         <v>78</v>
@@ -3063,19 +3075,19 @@
         <v>140</v>
       </c>
       <c r="F70" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G70" s="1">
-        <v>45978</v>
+        <v>44909</v>
       </c>
       <c r="H70" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I70" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J70" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -3086,28 +3098,28 @@
         <v>12</v>
       </c>
       <c r="C71">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D71" t="s">
         <v>79</v>
       </c>
       <c r="E71" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F71" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G71" s="1">
-        <v>45938</v>
+        <v>45978</v>
       </c>
       <c r="H71" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I71" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J71" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3118,28 +3130,28 @@
         <v>12</v>
       </c>
       <c r="C72">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="D72" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E72" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F72" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G72" s="1">
-        <v>46146</v>
+        <v>45938</v>
       </c>
       <c r="H72" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I72" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J72" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -3150,28 +3162,28 @@
         <v>12</v>
       </c>
       <c r="C73">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="D73" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E73" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F73" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G73" s="1">
-        <v>46076</v>
+        <v>46146</v>
       </c>
       <c r="H73" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I73" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J73" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3182,89 +3194,89 @@
         <v>12</v>
       </c>
       <c r="C74">
-        <v>127</v>
+        <v>213</v>
       </c>
       <c r="D74" t="s">
         <v>81</v>
       </c>
       <c r="E74" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F74" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G74" s="1">
-        <v>45444</v>
+        <v>46076</v>
       </c>
       <c r="H74" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I74" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J74" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
       </c>
       <c r="C75">
-        <v>1008</v>
+        <v>127</v>
       </c>
       <c r="D75" t="s">
         <v>82</v>
       </c>
       <c r="E75" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F75" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G75" s="1">
-        <v>46007</v>
+        <v>45444</v>
       </c>
       <c r="H75" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I75" t="s">
         <v>150</v>
       </c>
       <c r="J75" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B76" t="s">
         <v>12</v>
       </c>
       <c r="C76">
-        <v>214</v>
+        <v>1008</v>
       </c>
       <c r="D76" t="s">
         <v>83</v>
       </c>
       <c r="E76" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F76" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G76" s="1">
-        <v>46076</v>
+        <v>46007</v>
       </c>
       <c r="H76" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I76" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J76" t="s">
         <v>154</v>
@@ -3278,7 +3290,7 @@
         <v>12</v>
       </c>
       <c r="C77">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="D77" t="s">
         <v>84</v>
@@ -3287,19 +3299,19 @@
         <v>141</v>
       </c>
       <c r="F77" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G77" s="1">
-        <v>46197</v>
+        <v>46076</v>
       </c>
       <c r="H77" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I77" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J77" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -3316,19 +3328,19 @@
         <v>85</v>
       </c>
       <c r="E78" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F78" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G78" s="1">
         <v>45894</v>
       </c>
       <c r="H78" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I78" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J78" t="s">
         <v>159</v>
@@ -3348,22 +3360,22 @@
         <v>86</v>
       </c>
       <c r="E79" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F79" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G79" s="1">
         <v>44287</v>
       </c>
       <c r="H79" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I79" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J79" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -3380,22 +3392,22 @@
         <v>87</v>
       </c>
       <c r="E80" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F80" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G80" s="1">
         <v>45978</v>
       </c>
       <c r="H80" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I80" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J80" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -3412,19 +3424,19 @@
         <v>88</v>
       </c>
       <c r="E81" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F81" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G81" s="1">
         <v>44683</v>
       </c>
       <c r="H81" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I81" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J81" t="s">
         <v>159</v>
@@ -3444,22 +3456,22 @@
         <v>89</v>
       </c>
       <c r="E82" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F82" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G82" s="1">
         <v>46153</v>
       </c>
       <c r="H82" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I82" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J82" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -3476,22 +3488,22 @@
         <v>90</v>
       </c>
       <c r="E83" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F83" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G83" s="1">
         <v>45873</v>
       </c>
       <c r="H83" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I83" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J83" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -3508,22 +3520,22 @@
         <v>91</v>
       </c>
       <c r="E84" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F84" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G84" s="1">
         <v>45121</v>
       </c>
       <c r="H84" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I84" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J84" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -3540,22 +3552,22 @@
         <v>92</v>
       </c>
       <c r="E85" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F85" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G85" s="1">
         <v>45936</v>
       </c>
       <c r="H85" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I85" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J85" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -3572,22 +3584,22 @@
         <v>93</v>
       </c>
       <c r="E86" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F86" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G86" s="1">
         <v>45957</v>
       </c>
       <c r="H86" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I86" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J86" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -3604,22 +3616,22 @@
         <v>94</v>
       </c>
       <c r="E87" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F87" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G87" s="1">
         <v>44348</v>
       </c>
       <c r="H87" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I87" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J87" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/employees_CA.xlsx
+++ b/employees_CA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="164">
   <si>
     <t>Legal Name</t>
   </si>
@@ -106,9 +106,6 @@
     <t>Aixin</t>
   </si>
   <si>
-    <t>Zhengjie</t>
-  </si>
-  <si>
     <t>Bin</t>
   </si>
   <si>
@@ -332,9 +329,6 @@
   </si>
   <si>
     <t>Gu</t>
-  </si>
-  <si>
-    <t>Guan</t>
   </si>
   <si>
     <t>Guo</t>
@@ -847,7 +841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -896,22 +890,22 @@
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G2" s="1">
         <v>45916</v>
       </c>
       <c r="H2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I2" t="s">
         <v>148</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>150</v>
-      </c>
-      <c r="J2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -928,22 +922,22 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G3" s="1">
         <v>46230</v>
       </c>
       <c r="H3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J3" t="s">
         <v>151</v>
-      </c>
-      <c r="J3" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -960,22 +954,22 @@
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G4" s="1">
         <v>44929</v>
       </c>
       <c r="H4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -992,22 +986,22 @@
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G5" s="1">
         <v>46168</v>
       </c>
       <c r="H5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1024,22 +1018,22 @@
         <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G6" s="1">
         <v>43405</v>
       </c>
       <c r="H6" t="s">
+        <v>146</v>
+      </c>
+      <c r="I6" t="s">
         <v>148</v>
       </c>
-      <c r="I6" t="s">
-        <v>150</v>
-      </c>
       <c r="J6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1056,22 +1050,22 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G7" s="1">
         <v>45684</v>
       </c>
       <c r="H7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1088,22 +1082,22 @@
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G8" s="1">
         <v>46223</v>
       </c>
       <c r="H8" t="s">
+        <v>146</v>
+      </c>
+      <c r="I8" t="s">
         <v>148</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>150</v>
-      </c>
-      <c r="J8" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1120,22 +1114,22 @@
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G9" s="1">
         <v>45909</v>
       </c>
       <c r="H9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I9" t="s">
+        <v>149</v>
+      </c>
+      <c r="J9" t="s">
         <v>151</v>
-      </c>
-      <c r="J9" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1152,22 +1146,22 @@
         <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G10" s="1">
         <v>45471</v>
       </c>
       <c r="H10" t="s">
+        <v>146</v>
+      </c>
+      <c r="I10" t="s">
         <v>148</v>
       </c>
-      <c r="I10" t="s">
-        <v>150</v>
-      </c>
       <c r="J10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1184,22 +1178,22 @@
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G11" s="1">
         <v>45701</v>
       </c>
       <c r="H11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I11" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11" t="s">
         <v>151</v>
-      </c>
-      <c r="J11" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1216,22 +1210,22 @@
         <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G12" s="1">
         <v>46225</v>
       </c>
       <c r="H12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1248,22 +1242,22 @@
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G13" s="1">
         <v>45538</v>
       </c>
       <c r="H13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1280,22 +1274,22 @@
         <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F14" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G14" s="1">
         <v>45915</v>
       </c>
       <c r="H14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I14" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1312,22 +1306,22 @@
         <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G15" s="1">
         <v>44317</v>
       </c>
       <c r="H15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1344,22 +1338,22 @@
         <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G16" s="1">
         <v>45419</v>
       </c>
       <c r="H16" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" t="s">
         <v>148</v>
       </c>
-      <c r="I16" t="s">
-        <v>150</v>
-      </c>
       <c r="J16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1376,22 +1370,22 @@
         <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G17" s="1">
         <v>44069</v>
       </c>
       <c r="H17" t="s">
+        <v>146</v>
+      </c>
+      <c r="I17" t="s">
         <v>148</v>
       </c>
-      <c r="I17" t="s">
-        <v>150</v>
-      </c>
       <c r="J17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1408,22 +1402,22 @@
         <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F18" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G18" s="1">
         <v>44756</v>
       </c>
       <c r="H18" t="s">
+        <v>146</v>
+      </c>
+      <c r="I18" t="s">
         <v>148</v>
       </c>
-      <c r="I18" t="s">
-        <v>150</v>
-      </c>
       <c r="J18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1434,25 +1428,25 @@
         <v>12</v>
       </c>
       <c r="C19">
-        <v>237</v>
+        <v>2</v>
       </c>
       <c r="D19" t="s">
         <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G19" s="1">
-        <v>46252</v>
+        <v>44348</v>
       </c>
       <c r="H19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I19" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J19" t="s">
         <v>159</v>
@@ -1466,28 +1460,28 @@
         <v>12</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" t="s">
         <v>31</v>
       </c>
       <c r="E20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G20" s="1">
-        <v>44348</v>
+        <v>44452</v>
       </c>
       <c r="H20" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J20" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1498,28 +1492,28 @@
         <v>12</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>160</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G21" s="1">
-        <v>44452</v>
+        <v>45536</v>
       </c>
       <c r="H21" t="s">
+        <v>146</v>
+      </c>
+      <c r="I21" t="s">
         <v>148</v>
       </c>
-      <c r="I21" t="s">
-        <v>151</v>
-      </c>
       <c r="J21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1530,28 +1524,28 @@
         <v>12</v>
       </c>
       <c r="C22">
-        <v>160</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
         <v>33</v>
       </c>
       <c r="E22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F22" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G22" s="1">
-        <v>45536</v>
+        <v>44774</v>
       </c>
       <c r="H22" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I22" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J22" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1562,28 +1556,28 @@
         <v>12</v>
       </c>
       <c r="C23">
-        <v>38</v>
+        <v>225</v>
       </c>
       <c r="D23" t="s">
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F23" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G23" s="1">
-        <v>44774</v>
+        <v>46181</v>
       </c>
       <c r="H23" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I23" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J23" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1594,28 +1588,28 @@
         <v>12</v>
       </c>
       <c r="C24">
-        <v>225</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
         <v>35</v>
       </c>
       <c r="E24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F24" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G24" s="1">
-        <v>46181</v>
+        <v>43564</v>
       </c>
       <c r="H24" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I24" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J24" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1626,92 +1620,92 @@
         <v>12</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="D25" t="s">
         <v>36</v>
       </c>
       <c r="E25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F25" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G25" s="1">
-        <v>43564</v>
+        <v>44508</v>
       </c>
       <c r="H25" t="s">
+        <v>146</v>
+      </c>
+      <c r="I25" t="s">
         <v>148</v>
       </c>
-      <c r="I25" t="s">
-        <v>151</v>
-      </c>
       <c r="J25" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
       </c>
       <c r="C26">
-        <v>56</v>
+        <v>1044</v>
       </c>
       <c r="D26" t="s">
         <v>37</v>
       </c>
       <c r="E26" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="F26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G26" s="1">
-        <v>44508</v>
+        <v>45689</v>
       </c>
       <c r="H26" t="s">
+        <v>146</v>
+      </c>
+      <c r="I26" t="s">
         <v>148</v>
       </c>
-      <c r="I26" t="s">
-        <v>150</v>
-      </c>
       <c r="J26" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
       </c>
       <c r="C27">
-        <v>1044</v>
+        <v>60</v>
       </c>
       <c r="D27" t="s">
         <v>38</v>
       </c>
       <c r="E27" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="F27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G27" s="1">
-        <v>45689</v>
+        <v>44774</v>
       </c>
       <c r="H27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J27" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1722,28 +1716,28 @@
         <v>12</v>
       </c>
       <c r="C28">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="D28" t="s">
         <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F28" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G28" s="1">
-        <v>44774</v>
+        <v>45902</v>
       </c>
       <c r="H28" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I28" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J28" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1754,28 +1748,28 @@
         <v>12</v>
       </c>
       <c r="C29">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
         <v>40</v>
       </c>
       <c r="E29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F29" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G29" s="1">
-        <v>45902</v>
+        <v>45047</v>
       </c>
       <c r="H29" t="s">
+        <v>146</v>
+      </c>
+      <c r="I29" t="s">
         <v>148</v>
       </c>
-      <c r="I29" t="s">
-        <v>151</v>
-      </c>
       <c r="J29" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1786,28 +1780,28 @@
         <v>12</v>
       </c>
       <c r="C30">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="D30" t="s">
         <v>41</v>
       </c>
       <c r="E30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G30" s="1">
-        <v>45047</v>
+        <v>45859</v>
       </c>
       <c r="H30" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J30" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1818,28 +1812,28 @@
         <v>12</v>
       </c>
       <c r="C31">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D31" t="s">
         <v>42</v>
       </c>
       <c r="E31" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F31" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G31" s="1">
         <v>45859</v>
       </c>
       <c r="H31" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I31" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J31" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1850,28 +1844,28 @@
         <v>12</v>
       </c>
       <c r="C32">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D32" t="s">
         <v>43</v>
       </c>
       <c r="E32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F32" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G32" s="1">
-        <v>45859</v>
+        <v>45809</v>
       </c>
       <c r="H32" t="s">
+        <v>146</v>
+      </c>
+      <c r="I32" t="s">
         <v>148</v>
       </c>
-      <c r="I32" t="s">
-        <v>151</v>
-      </c>
       <c r="J32" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1882,28 +1876,28 @@
         <v>12</v>
       </c>
       <c r="C33">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F33" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G33" s="1">
-        <v>45809</v>
+        <v>46017</v>
       </c>
       <c r="H33" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I33" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J33" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1914,28 +1908,28 @@
         <v>12</v>
       </c>
       <c r="C34">
-        <v>208</v>
+        <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E34" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F34" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G34" s="1">
-        <v>46017</v>
+        <v>45313</v>
       </c>
       <c r="H34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I34" t="s">
+        <v>149</v>
+      </c>
+      <c r="J34" t="s">
         <v>151</v>
-      </c>
-      <c r="J34" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -1946,28 +1940,28 @@
         <v>12</v>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="D35" t="s">
         <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F35" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G35" s="1">
-        <v>45313</v>
+        <v>44858</v>
       </c>
       <c r="H35" t="s">
+        <v>146</v>
+      </c>
+      <c r="I35" t="s">
         <v>148</v>
       </c>
-      <c r="I35" t="s">
-        <v>151</v>
-      </c>
       <c r="J35" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1978,28 +1972,28 @@
         <v>12</v>
       </c>
       <c r="C36">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="D36" t="s">
         <v>46</v>
       </c>
       <c r="E36" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F36" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G36" s="1">
-        <v>44858</v>
+        <v>45600</v>
       </c>
       <c r="H36" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J36" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2010,25 +2004,25 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="D37" t="s">
         <v>47</v>
       </c>
       <c r="E37" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F37" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G37" s="1">
-        <v>45600</v>
+        <v>46197</v>
       </c>
       <c r="H37" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I37" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J37" t="s">
         <v>153</v>
@@ -2042,28 +2036,28 @@
         <v>12</v>
       </c>
       <c r="C38">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="D38" t="s">
         <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F38" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G38" s="1">
-        <v>46197</v>
+        <v>46113</v>
       </c>
       <c r="H38" t="s">
+        <v>146</v>
+      </c>
+      <c r="I38" t="s">
         <v>148</v>
       </c>
-      <c r="I38" t="s">
-        <v>151</v>
-      </c>
       <c r="J38" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2074,28 +2068,28 @@
         <v>12</v>
       </c>
       <c r="C39">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D39" t="s">
         <v>49</v>
       </c>
       <c r="E39" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F39" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G39" s="1">
-        <v>46113</v>
+        <v>46070</v>
       </c>
       <c r="H39" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I39" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J39" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2106,28 +2100,28 @@
         <v>12</v>
       </c>
       <c r="C40">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="D40" t="s">
         <v>50</v>
       </c>
       <c r="E40" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F40" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G40" s="1">
-        <v>46070</v>
+        <v>46254</v>
       </c>
       <c r="H40" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I40" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J40" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2138,25 +2132,25 @@
         <v>12</v>
       </c>
       <c r="C41">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="D41" t="s">
         <v>51</v>
       </c>
       <c r="E41" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F41" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G41" s="1">
-        <v>46254</v>
+        <v>46181</v>
       </c>
       <c r="H41" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I41" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J41" t="s">
         <v>155</v>
@@ -2170,28 +2164,28 @@
         <v>12</v>
       </c>
       <c r="C42">
-        <v>226</v>
+        <v>48</v>
       </c>
       <c r="D42" t="s">
         <v>52</v>
       </c>
       <c r="E42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F42" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G42" s="1">
-        <v>46181</v>
+        <v>44348</v>
       </c>
       <c r="H42" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I42" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J42" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2202,28 +2196,28 @@
         <v>12</v>
       </c>
       <c r="C43">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="D43" t="s">
         <v>53</v>
       </c>
       <c r="E43" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F43" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G43" s="1">
-        <v>44348</v>
+        <v>46126</v>
       </c>
       <c r="H43" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I43" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J43" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2234,28 +2228,28 @@
         <v>12</v>
       </c>
       <c r="C44">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="D44" t="s">
         <v>54</v>
       </c>
       <c r="E44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F44" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G44" s="1">
-        <v>46126</v>
+        <v>44802</v>
       </c>
       <c r="H44" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J44" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2266,28 +2260,28 @@
         <v>12</v>
       </c>
       <c r="C45">
-        <v>46</v>
+        <v>234</v>
       </c>
       <c r="D45" t="s">
         <v>55</v>
       </c>
       <c r="E45" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F45" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G45" s="1">
-        <v>44802</v>
+        <v>46237</v>
       </c>
       <c r="H45" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I45" t="s">
+        <v>149</v>
+      </c>
+      <c r="J45" t="s">
         <v>151</v>
-      </c>
-      <c r="J45" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2298,28 +2292,28 @@
         <v>12</v>
       </c>
       <c r="C46">
-        <v>234</v>
+        <v>141</v>
       </c>
       <c r="D46" t="s">
         <v>56</v>
       </c>
       <c r="E46" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F46" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G46" s="1">
-        <v>46237</v>
+        <v>45499</v>
       </c>
       <c r="H46" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I46" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J46" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2330,28 +2324,28 @@
         <v>12</v>
       </c>
       <c r="C47">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="D47" t="s">
         <v>57</v>
       </c>
       <c r="E47" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F47" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G47" s="1">
-        <v>45499</v>
+        <v>45957</v>
       </c>
       <c r="H47" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I47" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J47" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2362,28 +2356,28 @@
         <v>12</v>
       </c>
       <c r="C48">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="D48" t="s">
         <v>58</v>
       </c>
       <c r="E48" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F48" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G48" s="1">
-        <v>45957</v>
+        <v>43922</v>
       </c>
       <c r="H48" t="s">
+        <v>146</v>
+      </c>
+      <c r="I48" t="s">
         <v>148</v>
       </c>
-      <c r="I48" t="s">
-        <v>151</v>
-      </c>
       <c r="J48" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -2394,28 +2388,28 @@
         <v>12</v>
       </c>
       <c r="C49">
-        <v>15</v>
+        <v>165</v>
       </c>
       <c r="D49" t="s">
         <v>59</v>
       </c>
       <c r="E49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F49" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G49" s="1">
-        <v>43922</v>
+        <v>45579</v>
       </c>
       <c r="H49" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I49" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J49" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -2426,28 +2420,28 @@
         <v>12</v>
       </c>
       <c r="C50">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D50" t="s">
         <v>60</v>
       </c>
       <c r="E50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G50" s="1">
-        <v>45579</v>
+        <v>45509</v>
       </c>
       <c r="H50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I50" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J50" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2458,156 +2452,156 @@
         <v>12</v>
       </c>
       <c r="C51">
-        <v>147</v>
+        <v>235</v>
       </c>
       <c r="D51" t="s">
         <v>61</v>
       </c>
       <c r="E51" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F51" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G51" s="1">
-        <v>45509</v>
+        <v>46244</v>
       </c>
       <c r="H51" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I51" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J51" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
       </c>
       <c r="C52">
-        <v>235</v>
+        <v>1028</v>
       </c>
       <c r="D52" t="s">
         <v>62</v>
       </c>
       <c r="E52" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F52" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G52" s="1">
-        <v>46244</v>
+        <v>45239</v>
       </c>
       <c r="H52" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I52" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
       </c>
       <c r="C53">
-        <v>1028</v>
+        <v>85</v>
       </c>
       <c r="D53" t="s">
         <v>63</v>
       </c>
       <c r="E53" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F53" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G53" s="1">
-        <v>45239</v>
+        <v>46181</v>
       </c>
       <c r="H53" t="s">
+        <v>146</v>
+      </c>
+      <c r="I53" t="s">
         <v>148</v>
       </c>
-      <c r="I53" t="s">
-        <v>151</v>
-      </c>
       <c r="J53" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
       </c>
       <c r="C54">
-        <v>85</v>
+        <v>1043</v>
       </c>
       <c r="D54" t="s">
         <v>64</v>
       </c>
       <c r="E54" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F54" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G54" s="1">
-        <v>46181</v>
+        <v>45680</v>
       </c>
       <c r="H54" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I54" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J54" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
       </c>
       <c r="C55">
-        <v>1043</v>
+        <v>218</v>
       </c>
       <c r="D55" t="s">
         <v>65</v>
       </c>
       <c r="E55" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F55" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G55" s="1">
-        <v>45680</v>
+        <v>46127</v>
       </c>
       <c r="H55" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I55" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J55" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -2618,28 +2612,28 @@
         <v>12</v>
       </c>
       <c r="C56">
-        <v>218</v>
+        <v>176</v>
       </c>
       <c r="D56" t="s">
         <v>66</v>
       </c>
       <c r="E56" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G56" s="1">
-        <v>46127</v>
+        <v>45778</v>
       </c>
       <c r="H56" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I56" t="s">
+        <v>149</v>
+      </c>
+      <c r="J56" t="s">
         <v>151</v>
-      </c>
-      <c r="J56" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -2650,28 +2644,28 @@
         <v>12</v>
       </c>
       <c r="C57">
-        <v>176</v>
+        <v>41</v>
       </c>
       <c r="D57" t="s">
         <v>67</v>
       </c>
       <c r="E57" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G57" s="1">
-        <v>45778</v>
+        <v>44537</v>
       </c>
       <c r="H57" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I57" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J57" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -2682,220 +2676,220 @@
         <v>12</v>
       </c>
       <c r="C58">
-        <v>41</v>
+        <v>233</v>
       </c>
       <c r="D58" t="s">
         <v>68</v>
       </c>
       <c r="E58" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F58" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G58" s="1">
-        <v>44537</v>
+        <v>46237</v>
       </c>
       <c r="H58" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I58" t="s">
+        <v>149</v>
+      </c>
+      <c r="J58" t="s">
         <v>151</v>
-      </c>
-      <c r="J58" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
       </c>
       <c r="C59">
-        <v>233</v>
+        <v>1017</v>
       </c>
       <c r="D59" t="s">
         <v>69</v>
       </c>
       <c r="E59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F59" t="s">
+        <v>145</v>
+      </c>
+      <c r="G59" s="1">
+        <v>45062</v>
+      </c>
+      <c r="H59" t="s">
         <v>147</v>
       </c>
-      <c r="G59" s="1">
-        <v>46237</v>
-      </c>
-      <c r="H59" t="s">
+      <c r="I59" t="s">
         <v>148</v>
       </c>
-      <c r="I59" t="s">
-        <v>151</v>
-      </c>
       <c r="J59" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B60" t="s">
         <v>12</v>
       </c>
       <c r="C60">
-        <v>1017</v>
+        <v>166</v>
       </c>
       <c r="D60" t="s">
         <v>70</v>
       </c>
       <c r="E60" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F60" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G60" s="1">
-        <v>45062</v>
+        <v>45586</v>
       </c>
       <c r="H60" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I60" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J60" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
       </c>
       <c r="C61">
-        <v>166</v>
+        <v>1041</v>
       </c>
       <c r="D61" t="s">
         <v>71</v>
       </c>
       <c r="E61" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F61" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G61" s="1">
-        <v>45586</v>
+        <v>45689</v>
       </c>
       <c r="H61" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I61" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J61" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
       </c>
       <c r="C62">
-        <v>1041</v>
+        <v>209</v>
       </c>
       <c r="D62" t="s">
         <v>72</v>
       </c>
       <c r="E62" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F62" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G62" s="1">
-        <v>45689</v>
+        <v>46048</v>
       </c>
       <c r="H62" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I62" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J62" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
       </c>
       <c r="C63">
-        <v>209</v>
+        <v>1027</v>
       </c>
       <c r="D63" t="s">
         <v>73</v>
       </c>
       <c r="E63" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F63" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G63" s="1">
-        <v>46048</v>
+        <v>45176</v>
       </c>
       <c r="H63" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I63" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J63" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
       </c>
       <c r="C64">
-        <v>1027</v>
+        <v>21</v>
       </c>
       <c r="D64" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="E64" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F64" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G64" s="1">
-        <v>45176</v>
+        <v>45243</v>
       </c>
       <c r="H64" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I64" t="s">
+        <v>149</v>
+      </c>
+      <c r="J64" t="s">
         <v>151</v>
-      </c>
-      <c r="J64" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -2906,89 +2900,89 @@
         <v>12</v>
       </c>
       <c r="C65">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="D65" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E65" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F65" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G65" s="1">
-        <v>45243</v>
+        <v>46141</v>
       </c>
       <c r="H65" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I65" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J65" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
       </c>
       <c r="C66">
-        <v>220</v>
+        <v>1013</v>
       </c>
       <c r="D66" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="E66" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F66" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G66" s="1">
-        <v>46141</v>
+        <v>44929</v>
       </c>
       <c r="H66" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I66" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J66" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
       </c>
       <c r="C67">
-        <v>1013</v>
+        <v>223</v>
       </c>
       <c r="D67" t="s">
         <v>75</v>
       </c>
       <c r="E67" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F67" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G67" s="1">
-        <v>44929</v>
+        <v>46163</v>
       </c>
       <c r="H67" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I67" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J67" t="s">
         <v>154</v>
@@ -3002,28 +2996,28 @@
         <v>12</v>
       </c>
       <c r="C68">
-        <v>223</v>
+        <v>121</v>
       </c>
       <c r="D68" t="s">
         <v>76</v>
       </c>
       <c r="E68" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F68" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G68" s="1">
-        <v>46163</v>
+        <v>45432</v>
       </c>
       <c r="H68" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I68" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J68" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -3034,28 +3028,28 @@
         <v>12</v>
       </c>
       <c r="C69">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="D69" t="s">
         <v>77</v>
       </c>
       <c r="E69" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F69" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G69" s="1">
-        <v>45432</v>
+        <v>44909</v>
       </c>
       <c r="H69" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I69" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J69" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -3066,28 +3060,28 @@
         <v>12</v>
       </c>
       <c r="C70">
-        <v>65</v>
+        <v>205</v>
       </c>
       <c r="D70" t="s">
         <v>78</v>
       </c>
       <c r="E70" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F70" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G70" s="1">
-        <v>44909</v>
+        <v>45978</v>
       </c>
       <c r="H70" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I70" t="s">
+        <v>149</v>
+      </c>
+      <c r="J70" t="s">
         <v>151</v>
-      </c>
-      <c r="J70" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -3098,28 +3092,28 @@
         <v>12</v>
       </c>
       <c r="C71">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D71" t="s">
         <v>79</v>
       </c>
       <c r="E71" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F71" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G71" s="1">
-        <v>45978</v>
+        <v>45938</v>
       </c>
       <c r="H71" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I71" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J71" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3130,28 +3124,28 @@
         <v>12</v>
       </c>
       <c r="C72">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="D72" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E72" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F72" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G72" s="1">
-        <v>45938</v>
+        <v>46146</v>
       </c>
       <c r="H72" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I72" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J72" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -3162,28 +3156,28 @@
         <v>12</v>
       </c>
       <c r="C73">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D73" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E73" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F73" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G73" s="1">
-        <v>46146</v>
+        <v>46076</v>
       </c>
       <c r="H73" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I73" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J73" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3194,57 +3188,57 @@
         <v>12</v>
       </c>
       <c r="C74">
-        <v>213</v>
+        <v>127</v>
       </c>
       <c r="D74" t="s">
         <v>81</v>
       </c>
       <c r="E74" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F74" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G74" s="1">
-        <v>46076</v>
+        <v>45444</v>
       </c>
       <c r="H74" t="s">
+        <v>146</v>
+      </c>
+      <c r="I74" t="s">
         <v>148</v>
       </c>
-      <c r="I74" t="s">
-        <v>151</v>
-      </c>
       <c r="J74" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
       </c>
       <c r="C75">
-        <v>127</v>
+        <v>1008</v>
       </c>
       <c r="D75" t="s">
         <v>82</v>
       </c>
       <c r="E75" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F75" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G75" s="1">
-        <v>45444</v>
+        <v>46007</v>
       </c>
       <c r="H75" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I75" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J75" t="s">
         <v>152</v>
@@ -3252,34 +3246,34 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B76" t="s">
         <v>12</v>
       </c>
       <c r="C76">
-        <v>1008</v>
+        <v>214</v>
       </c>
       <c r="D76" t="s">
         <v>83</v>
       </c>
       <c r="E76" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F76" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G76" s="1">
-        <v>46007</v>
+        <v>46076</v>
       </c>
       <c r="H76" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I76" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J76" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3290,28 +3284,28 @@
         <v>12</v>
       </c>
       <c r="C77">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="D77" t="s">
         <v>84</v>
       </c>
       <c r="E77" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F77" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G77" s="1">
-        <v>46076</v>
+        <v>45894</v>
       </c>
       <c r="H77" t="s">
+        <v>146</v>
+      </c>
+      <c r="I77" t="s">
         <v>148</v>
       </c>
-      <c r="I77" t="s">
-        <v>151</v>
-      </c>
       <c r="J77" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -3322,25 +3316,25 @@
         <v>12</v>
       </c>
       <c r="C78">
-        <v>189</v>
+        <v>9</v>
       </c>
       <c r="D78" t="s">
         <v>85</v>
       </c>
       <c r="E78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F78" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G78" s="1">
-        <v>45894</v>
+        <v>44287</v>
       </c>
       <c r="H78" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I78" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J78" t="s">
         <v>159</v>
@@ -3354,28 +3348,28 @@
         <v>12</v>
       </c>
       <c r="C79">
-        <v>9</v>
+        <v>204</v>
       </c>
       <c r="D79" t="s">
         <v>86</v>
       </c>
       <c r="E79" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F79" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G79" s="1">
-        <v>44287</v>
+        <v>45978</v>
       </c>
       <c r="H79" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I79" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J79" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -3386,28 +3380,28 @@
         <v>12</v>
       </c>
       <c r="C80">
-        <v>204</v>
+        <v>22</v>
       </c>
       <c r="D80" t="s">
         <v>87</v>
       </c>
       <c r="E80" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F80" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G80" s="1">
-        <v>45978</v>
+        <v>44683</v>
       </c>
       <c r="H80" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I80" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J80" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -3418,28 +3412,28 @@
         <v>12</v>
       </c>
       <c r="C81">
-        <v>22</v>
+        <v>228</v>
       </c>
       <c r="D81" t="s">
         <v>88</v>
       </c>
       <c r="E81" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F81" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G81" s="1">
-        <v>44683</v>
+        <v>46153</v>
       </c>
       <c r="H81" t="s">
+        <v>146</v>
+      </c>
+      <c r="I81" t="s">
         <v>148</v>
       </c>
-      <c r="I81" t="s">
-        <v>151</v>
-      </c>
       <c r="J81" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -3450,28 +3444,28 @@
         <v>12</v>
       </c>
       <c r="C82">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="D82" t="s">
         <v>89</v>
       </c>
       <c r="E82" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F82" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G82" s="1">
-        <v>46153</v>
+        <v>45873</v>
       </c>
       <c r="H82" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I82" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J82" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -3482,25 +3476,25 @@
         <v>12</v>
       </c>
       <c r="C83">
-        <v>187</v>
+        <v>84</v>
       </c>
       <c r="D83" t="s">
         <v>90</v>
       </c>
       <c r="E83" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F83" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G83" s="1">
-        <v>45873</v>
+        <v>45121</v>
       </c>
       <c r="H83" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I83" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J83" t="s">
         <v>153</v>
@@ -3514,28 +3508,28 @@
         <v>12</v>
       </c>
       <c r="C84">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="D84" t="s">
         <v>91</v>
       </c>
       <c r="E84" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F84" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G84" s="1">
-        <v>45121</v>
+        <v>45936</v>
       </c>
       <c r="H84" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I84" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J84" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -3546,28 +3540,28 @@
         <v>12</v>
       </c>
       <c r="C85">
-        <v>198</v>
+        <v>133</v>
       </c>
       <c r="D85" t="s">
         <v>92</v>
       </c>
       <c r="E85" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F85" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G85" s="1">
-        <v>45936</v>
+        <v>45957</v>
       </c>
       <c r="H85" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I85" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J85" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -3578,60 +3572,28 @@
         <v>12</v>
       </c>
       <c r="C86">
-        <v>133</v>
+        <v>3</v>
       </c>
       <c r="D86" t="s">
         <v>93</v>
       </c>
       <c r="E86" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F86" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G86" s="1">
-        <v>45957</v>
+        <v>44348</v>
       </c>
       <c r="H86" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I86" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J86" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
-      <c r="A87" t="s">
-        <v>10</v>
-      </c>
-      <c r="B87" t="s">
-        <v>12</v>
-      </c>
-      <c r="C87">
-        <v>3</v>
-      </c>
-      <c r="D87" t="s">
-        <v>94</v>
-      </c>
-      <c r="E87" t="s">
-        <v>146</v>
-      </c>
-      <c r="F87" t="s">
-        <v>147</v>
-      </c>
-      <c r="G87" s="1">
-        <v>44348</v>
-      </c>
-      <c r="H87" t="s">
-        <v>148</v>
-      </c>
-      <c r="I87" t="s">
-        <v>151</v>
-      </c>
-      <c r="J87" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/employees_CA.xlsx
+++ b/employees_CA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="164">
   <si>
     <t>Legal Name</t>
   </si>
@@ -61,243 +61,246 @@
     <t>Xinyi</t>
   </si>
   <si>
+    <t>Hong</t>
+  </si>
+  <si>
+    <t>Jian</t>
+  </si>
+  <si>
+    <t>Yixiong</t>
+  </si>
+  <si>
+    <t>Zhenjun</t>
+  </si>
+  <si>
+    <t>Qingzi</t>
+  </si>
+  <si>
+    <t>Weixia</t>
+  </si>
+  <si>
+    <t>Xiaolong</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>Huali</t>
+  </si>
+  <si>
+    <t>Yankun</t>
+  </si>
+  <si>
+    <t>Ya-Mei</t>
+  </si>
+  <si>
+    <t>Hui</t>
+  </si>
+  <si>
+    <t>Aixin</t>
+  </si>
+  <si>
+    <t>Bin</t>
+  </si>
+  <si>
+    <t>Chunpeng</t>
+  </si>
+  <si>
+    <t>Bing</t>
+  </si>
+  <si>
+    <t>Xixing</t>
+  </si>
+  <si>
+    <t>Wenhu</t>
+  </si>
+  <si>
+    <t>Enquan</t>
+  </si>
+  <si>
+    <t>Ting</t>
+  </si>
+  <si>
+    <t>Jia-Huei</t>
+  </si>
+  <si>
+    <t>KunIengCheong</t>
+  </si>
+  <si>
+    <t>Enduo</t>
+  </si>
+  <si>
+    <t>Guanzhong</t>
+  </si>
+  <si>
+    <t>Jie</t>
+  </si>
+  <si>
+    <t>Zhihong</t>
+  </si>
+  <si>
+    <t>Yaodong</t>
+  </si>
+  <si>
+    <t>Chunyang</t>
+  </si>
+  <si>
+    <t>Emily</t>
+  </si>
+  <si>
+    <t>Jing</t>
+  </si>
+  <si>
+    <t>Xiaoyang</t>
+  </si>
+  <si>
+    <t>Xin</t>
+  </si>
+  <si>
+    <t>Yinli</t>
+  </si>
+  <si>
+    <t>Zhilong</t>
+  </si>
+  <si>
+    <t>Arze</t>
+  </si>
+  <si>
+    <t>HAIBO</t>
+  </si>
+  <si>
+    <t>Yuwei</t>
+  </si>
+  <si>
+    <t>Boyu</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>Zhiyi</t>
+  </si>
+  <si>
+    <t>Guillermo F</t>
+  </si>
+  <si>
+    <t>Guanqi</t>
+  </si>
+  <si>
+    <t>Jaime</t>
+  </si>
+  <si>
+    <t>Yanting</t>
+  </si>
+  <si>
+    <t>Yinghui</t>
+  </si>
+  <si>
+    <t>Wingking</t>
+  </si>
+  <si>
+    <t>Tip Wa</t>
+  </si>
+  <si>
+    <t>Yi</t>
+  </si>
+  <si>
+    <t>German D</t>
+  </si>
+  <si>
+    <t>Weidong</t>
+  </si>
+  <si>
+    <t>Libang</t>
+  </si>
+  <si>
+    <t>Ronghua</t>
+  </si>
+  <si>
+    <t>Ya-Han</t>
+  </si>
+  <si>
+    <t>Zhen</t>
+  </si>
+  <si>
+    <t>Guang</t>
+  </si>
+  <si>
+    <t>Ming</t>
+  </si>
+  <si>
+    <t>Xurong</t>
+  </si>
+  <si>
+    <t>Yihui</t>
+  </si>
+  <si>
+    <t>Yiyu</t>
+  </si>
+  <si>
+    <t>Yuran</t>
+  </si>
+  <si>
+    <t>Qianyang</t>
+  </si>
+  <si>
+    <t>Gang</t>
+  </si>
+  <si>
+    <t>Haiqiang</t>
+  </si>
+  <si>
+    <t>Jinping</t>
+  </si>
+  <si>
+    <t>Xiaqing</t>
+  </si>
+  <si>
+    <t>Yuhua</t>
+  </si>
+  <si>
+    <t>Xidong</t>
+  </si>
+  <si>
+    <t>Yalin</t>
+  </si>
+  <si>
+    <t>Minlin</t>
+  </si>
+  <si>
+    <t>Changqing</t>
+  </si>
+  <si>
     <t>David</t>
   </si>
   <si>
-    <t>Hong</t>
-  </si>
-  <si>
-    <t>Jian</t>
-  </si>
-  <si>
     <t>Ye</t>
   </si>
   <si>
-    <t>Yixiong</t>
-  </si>
-  <si>
-    <t>Zhenjun</t>
-  </si>
-  <si>
-    <t>Qingzi</t>
-  </si>
-  <si>
-    <t>Weixia</t>
-  </si>
-  <si>
-    <t>Xiaolong</t>
-  </si>
-  <si>
-    <t>Anna</t>
-  </si>
-  <si>
-    <t>Huali</t>
-  </si>
-  <si>
-    <t>Yankun</t>
-  </si>
-  <si>
-    <t>Ya-Mei</t>
-  </si>
-  <si>
-    <t>Hui</t>
-  </si>
-  <si>
-    <t>Aixin</t>
-  </si>
-  <si>
-    <t>Bin</t>
-  </si>
-  <si>
-    <t>Chunpeng</t>
-  </si>
-  <si>
-    <t>Bing</t>
-  </si>
-  <si>
-    <t>Xixing</t>
-  </si>
-  <si>
-    <t>Wenhu</t>
-  </si>
-  <si>
-    <t>Enquan</t>
-  </si>
-  <si>
-    <t>Ting</t>
-  </si>
-  <si>
     <t>Jiu</t>
   </si>
   <si>
-    <t>KunIengCheong</t>
-  </si>
-  <si>
-    <t>Enduo</t>
-  </si>
-  <si>
-    <t>Guanzhong</t>
-  </si>
-  <si>
-    <t>Jie</t>
-  </si>
-  <si>
-    <t>Zhihong</t>
-  </si>
-  <si>
-    <t>Yaodong</t>
-  </si>
-  <si>
-    <t>Chunyang</t>
-  </si>
-  <si>
-    <t>Emily</t>
-  </si>
-  <si>
-    <t>Jing</t>
-  </si>
-  <si>
-    <t>Xiaoyang</t>
-  </si>
-  <si>
-    <t>Xin</t>
-  </si>
-  <si>
-    <t>Yinli</t>
-  </si>
-  <si>
-    <t>Zhilong</t>
-  </si>
-  <si>
-    <t>Arze</t>
-  </si>
-  <si>
-    <t>HAIBO</t>
-  </si>
-  <si>
-    <t>Yuwei</t>
-  </si>
-  <si>
-    <t>Boyu</t>
-  </si>
-  <si>
-    <t>Jose</t>
-  </si>
-  <si>
-    <t>Zhiyi</t>
-  </si>
-  <si>
-    <t>Guillermo F</t>
-  </si>
-  <si>
-    <t>Huanyu</t>
-  </si>
-  <si>
-    <t>Guanqi</t>
-  </si>
-  <si>
-    <t>Jaime</t>
-  </si>
-  <si>
-    <t>Yanting</t>
-  </si>
-  <si>
     <t>Lanlan</t>
   </si>
   <si>
-    <t>Yinghui</t>
-  </si>
-  <si>
     <t>Zhaoyi</t>
   </si>
   <si>
-    <t>Wingking</t>
-  </si>
-  <si>
-    <t>Tip Wa</t>
-  </si>
-  <si>
-    <t>Yi</t>
-  </si>
-  <si>
-    <t>German D</t>
-  </si>
-  <si>
     <t>Ying</t>
   </si>
   <si>
-    <t>Weidong</t>
-  </si>
-  <si>
     <t>Lexi</t>
   </si>
   <si>
-    <t>Libang</t>
-  </si>
-  <si>
     <t>Yujian</t>
   </si>
   <si>
     <t>Xiangju</t>
   </si>
   <si>
-    <t>Ya-Han</t>
-  </si>
-  <si>
-    <t>Zhen</t>
-  </si>
-  <si>
-    <t>Guang</t>
-  </si>
-  <si>
-    <t>Ming</t>
-  </si>
-  <si>
-    <t>Xurong</t>
-  </si>
-  <si>
-    <t>Yihui</t>
-  </si>
-  <si>
-    <t>Yiyu</t>
-  </si>
-  <si>
     <t>Yue</t>
   </si>
   <si>
-    <t>Yuran</t>
-  </si>
-  <si>
-    <t>Qianyang</t>
-  </si>
-  <si>
-    <t>Gang</t>
-  </si>
-  <si>
-    <t>Haiqiang</t>
-  </si>
-  <si>
-    <t>Jinping</t>
-  </si>
-  <si>
-    <t>Xiaqing</t>
-  </si>
-  <si>
-    <t>Yuhua</t>
-  </si>
-  <si>
-    <t>Xidong</t>
-  </si>
-  <si>
-    <t>Yalin</t>
-  </si>
-  <si>
-    <t>Minlin</t>
-  </si>
-  <si>
-    <t>Changqing</t>
-  </si>
-  <si>
     <t>Bian</t>
   </si>
   <si>
@@ -382,9 +385,6 @@
     <t>Narvaez Fonseca</t>
   </si>
   <si>
-    <t>Ning</t>
-  </si>
-  <si>
     <t>Qu</t>
   </si>
   <si>
@@ -409,48 +409,48 @@
     <t>Vasquez Ortiz</t>
   </si>
   <si>
+    <t>Wei</t>
+  </si>
+  <si>
+    <t>Xia</t>
+  </si>
+  <si>
+    <t>Xu</t>
+  </si>
+  <si>
+    <t>Yang</t>
+  </si>
+  <si>
+    <t>Yu</t>
+  </si>
+  <si>
+    <t>Zhang</t>
+  </si>
+  <si>
+    <t>Zhao</t>
+  </si>
+  <si>
+    <t>Zheng</t>
+  </si>
+  <si>
+    <t>Zhou</t>
+  </si>
+  <si>
+    <t>Zhuang</t>
+  </si>
+  <si>
+    <t>Zou</t>
+  </si>
+  <si>
     <t>Wang</t>
   </si>
   <si>
-    <t>Wei</t>
-  </si>
-  <si>
     <t>Winstone</t>
   </si>
   <si>
-    <t>Xia</t>
-  </si>
-  <si>
     <t>Xiong</t>
   </si>
   <si>
-    <t>Xu</t>
-  </si>
-  <si>
-    <t>Yang</t>
-  </si>
-  <si>
-    <t>Yu</t>
-  </si>
-  <si>
-    <t>Zhang</t>
-  </si>
-  <si>
-    <t>Zhao</t>
-  </si>
-  <si>
-    <t>Zheng</t>
-  </si>
-  <si>
-    <t>Zhou</t>
-  </si>
-  <si>
-    <t>Zhuang</t>
-  </si>
-  <si>
-    <t>Zou</t>
-  </si>
-  <si>
     <t>Active</t>
   </si>
   <si>
@@ -472,40 +472,40 @@
     <t>Inventory - Department Inventory</t>
   </si>
   <si>
+    <t>Outbound - Department Outbound</t>
+  </si>
+  <si>
+    <t>HR - HR</t>
+  </si>
+  <si>
+    <t>QC - QC</t>
+  </si>
+  <si>
+    <t>Finance - Department Finance</t>
+  </si>
+  <si>
+    <t>Dispatch - Dispatching Center</t>
+  </si>
+  <si>
+    <t>CS - Department CS</t>
+  </si>
+  <si>
+    <t>Inbound - Department Inbound</t>
+  </si>
+  <si>
+    <t>Receiving - Receiving</t>
+  </si>
+  <si>
+    <t>MS - Department MS</t>
+  </si>
+  <si>
+    <t>Resource - Resource Center</t>
+  </si>
+  <si>
+    <t>Product - Department Product</t>
+  </si>
+  <si>
     <t>Drop-Shipp - Drop-Shipping</t>
-  </si>
-  <si>
-    <t>Outbound - Department Outbound</t>
-  </si>
-  <si>
-    <t>HR - HR</t>
-  </si>
-  <si>
-    <t>QC - QC</t>
-  </si>
-  <si>
-    <t>Finance - Department Finance</t>
-  </si>
-  <si>
-    <t>Dispatch - Dispatching Center</t>
-  </si>
-  <si>
-    <t>CS - Department CS</t>
-  </si>
-  <si>
-    <t>Inbound - Department Inbound</t>
-  </si>
-  <si>
-    <t>Receiving - Receiving</t>
-  </si>
-  <si>
-    <t>MS - Department MS</t>
-  </si>
-  <si>
-    <t>Resource - Resource Center</t>
-  </si>
-  <si>
-    <t>Product - Department Product</t>
   </si>
 </sst>
 </file>
@@ -841,7 +841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -890,7 +890,7 @@
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F2" t="s">
         <v>145</v>
@@ -922,7 +922,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F3" t="s">
         <v>145</v>
@@ -942,25 +942,25 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4">
-        <v>1012</v>
+        <v>224</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F4" t="s">
         <v>145</v>
       </c>
       <c r="G4" s="1">
-        <v>44929</v>
+        <v>46168</v>
       </c>
       <c r="H4" t="s">
         <v>146</v>
@@ -980,25 +980,25 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>224</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F5" t="s">
         <v>145</v>
       </c>
       <c r="G5" s="1">
-        <v>46168</v>
+        <v>43405</v>
       </c>
       <c r="H5" t="s">
         <v>146</v>
       </c>
       <c r="I5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J5" t="s">
         <v>153</v>
@@ -1012,19 +1012,19 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>236</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F6" t="s">
         <v>145</v>
       </c>
       <c r="G6" s="1">
-        <v>43405</v>
+        <v>46223</v>
       </c>
       <c r="H6" t="s">
         <v>146</v>
@@ -1033,30 +1033,30 @@
         <v>148</v>
       </c>
       <c r="J6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7">
-        <v>1040</v>
+        <v>191</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F7" t="s">
         <v>145</v>
       </c>
       <c r="G7" s="1">
-        <v>45684</v>
+        <v>45909</v>
       </c>
       <c r="H7" t="s">
         <v>146</v>
@@ -1065,7 +1065,7 @@
         <v>149</v>
       </c>
       <c r="J7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1076,19 +1076,19 @@
         <v>12</v>
       </c>
       <c r="C8">
-        <v>236</v>
+        <v>129</v>
       </c>
       <c r="D8" t="s">
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F8" t="s">
         <v>145</v>
       </c>
       <c r="G8" s="1">
-        <v>46223</v>
+        <v>45471</v>
       </c>
       <c r="H8" t="s">
         <v>146</v>
@@ -1097,7 +1097,7 @@
         <v>148</v>
       </c>
       <c r="J8" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1108,19 +1108,19 @@
         <v>12</v>
       </c>
       <c r="C9">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F9" t="s">
         <v>145</v>
       </c>
       <c r="G9" s="1">
-        <v>45909</v>
+        <v>45701</v>
       </c>
       <c r="H9" t="s">
         <v>146</v>
@@ -1140,28 +1140,28 @@
         <v>12</v>
       </c>
       <c r="C10">
-        <v>129</v>
+        <v>231</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F10" t="s">
         <v>145</v>
       </c>
       <c r="G10" s="1">
-        <v>45471</v>
+        <v>46225</v>
       </c>
       <c r="H10" t="s">
         <v>146</v>
       </c>
       <c r="I10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1172,19 +1172,19 @@
         <v>12</v>
       </c>
       <c r="C11">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="D11" t="s">
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F11" t="s">
         <v>145</v>
       </c>
       <c r="G11" s="1">
-        <v>45701</v>
+        <v>45538</v>
       </c>
       <c r="H11" t="s">
         <v>146</v>
@@ -1193,7 +1193,7 @@
         <v>149</v>
       </c>
       <c r="J11" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1204,19 +1204,19 @@
         <v>12</v>
       </c>
       <c r="C12">
-        <v>231</v>
+        <v>193</v>
       </c>
       <c r="D12" t="s">
         <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F12" t="s">
         <v>145</v>
       </c>
       <c r="G12" s="1">
-        <v>46225</v>
+        <v>45915</v>
       </c>
       <c r="H12" t="s">
         <v>146</v>
@@ -1225,7 +1225,7 @@
         <v>149</v>
       </c>
       <c r="J12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1236,19 +1236,19 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>154</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F13" t="s">
         <v>145</v>
       </c>
       <c r="G13" s="1">
-        <v>45538</v>
+        <v>44317</v>
       </c>
       <c r="H13" t="s">
         <v>146</v>
@@ -1268,28 +1268,28 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
         <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F14" t="s">
         <v>145</v>
       </c>
       <c r="G14" s="1">
-        <v>45915</v>
+        <v>45419</v>
       </c>
       <c r="H14" t="s">
         <v>146</v>
       </c>
       <c r="I14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J14" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1300,25 +1300,25 @@
         <v>12</v>
       </c>
       <c r="C15">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F15" t="s">
         <v>145</v>
       </c>
       <c r="G15" s="1">
-        <v>44317</v>
+        <v>44069</v>
       </c>
       <c r="H15" t="s">
         <v>146</v>
       </c>
       <c r="I15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J15" t="s">
         <v>157</v>
@@ -1332,19 +1332,19 @@
         <v>12</v>
       </c>
       <c r="C16">
-        <v>119</v>
+        <v>1</v>
       </c>
       <c r="D16" t="s">
         <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F16" t="s">
         <v>145</v>
       </c>
       <c r="G16" s="1">
-        <v>45419</v>
+        <v>44756</v>
       </c>
       <c r="H16" t="s">
         <v>146</v>
@@ -1353,7 +1353,7 @@
         <v>148</v>
       </c>
       <c r="J16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1364,25 +1364,25 @@
         <v>12</v>
       </c>
       <c r="C17">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F17" t="s">
         <v>145</v>
       </c>
       <c r="G17" s="1">
-        <v>44069</v>
+        <v>44348</v>
       </c>
       <c r="H17" t="s">
         <v>146</v>
       </c>
       <c r="I17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J17" t="s">
         <v>158</v>
@@ -1396,28 +1396,28 @@
         <v>12</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" t="s">
         <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F18" t="s">
         <v>145</v>
       </c>
       <c r="G18" s="1">
-        <v>44756</v>
+        <v>44452</v>
       </c>
       <c r="H18" t="s">
         <v>146</v>
       </c>
       <c r="I18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J18" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1428,28 +1428,28 @@
         <v>12</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="D19" t="s">
         <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F19" t="s">
         <v>145</v>
       </c>
       <c r="G19" s="1">
-        <v>44348</v>
+        <v>45536</v>
       </c>
       <c r="H19" t="s">
         <v>146</v>
       </c>
       <c r="I19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J19" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1460,19 +1460,19 @@
         <v>12</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
         <v>31</v>
       </c>
       <c r="E20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F20" t="s">
         <v>145</v>
       </c>
       <c r="G20" s="1">
-        <v>44452</v>
+        <v>44774</v>
       </c>
       <c r="H20" t="s">
         <v>146</v>
@@ -1481,7 +1481,7 @@
         <v>149</v>
       </c>
       <c r="J20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1492,28 +1492,28 @@
         <v>12</v>
       </c>
       <c r="C21">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F21" t="s">
         <v>145</v>
       </c>
       <c r="G21" s="1">
-        <v>45536</v>
+        <v>46181</v>
       </c>
       <c r="H21" t="s">
         <v>146</v>
       </c>
       <c r="I21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J21" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1524,19 +1524,19 @@
         <v>12</v>
       </c>
       <c r="C22">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="D22" t="s">
         <v>33</v>
       </c>
       <c r="E22" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F22" t="s">
         <v>145</v>
       </c>
       <c r="G22" s="1">
-        <v>44774</v>
+        <v>43564</v>
       </c>
       <c r="H22" t="s">
         <v>146</v>
@@ -1545,7 +1545,7 @@
         <v>149</v>
       </c>
       <c r="J22" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1556,28 +1556,28 @@
         <v>12</v>
       </c>
       <c r="C23">
-        <v>225</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F23" t="s">
         <v>145</v>
       </c>
       <c r="G23" s="1">
-        <v>46181</v>
+        <v>44508</v>
       </c>
       <c r="H23" t="s">
         <v>146</v>
       </c>
       <c r="I23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1588,19 +1588,19 @@
         <v>12</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>239</v>
       </c>
       <c r="D24" t="s">
         <v>35</v>
       </c>
       <c r="E24" t="s">
-        <v>108</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
         <v>145</v>
       </c>
       <c r="G24" s="1">
-        <v>43564</v>
+        <v>46265</v>
       </c>
       <c r="H24" t="s">
         <v>146</v>
@@ -1609,7 +1609,7 @@
         <v>149</v>
       </c>
       <c r="J24" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1620,60 +1620,60 @@
         <v>12</v>
       </c>
       <c r="C25">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
         <v>36</v>
       </c>
       <c r="E25" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F25" t="s">
         <v>145</v>
       </c>
       <c r="G25" s="1">
-        <v>44508</v>
+        <v>44774</v>
       </c>
       <c r="H25" t="s">
         <v>146</v>
       </c>
       <c r="I25" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J25" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
       </c>
       <c r="C26">
-        <v>1044</v>
+        <v>190</v>
       </c>
       <c r="D26" t="s">
         <v>37</v>
       </c>
       <c r="E26" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="F26" t="s">
         <v>145</v>
       </c>
       <c r="G26" s="1">
-        <v>45689</v>
+        <v>45902</v>
       </c>
       <c r="H26" t="s">
         <v>146</v>
       </c>
       <c r="I26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J26" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1684,28 +1684,28 @@
         <v>12</v>
       </c>
       <c r="C27">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
         <v>38</v>
       </c>
       <c r="E27" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F27" t="s">
         <v>145</v>
       </c>
       <c r="G27" s="1">
-        <v>44774</v>
+        <v>45047</v>
       </c>
       <c r="H27" t="s">
         <v>146</v>
       </c>
       <c r="I27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J27" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1716,19 +1716,19 @@
         <v>12</v>
       </c>
       <c r="C28">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D28" t="s">
         <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" t="s">
         <v>145</v>
       </c>
       <c r="G28" s="1">
-        <v>45902</v>
+        <v>45859</v>
       </c>
       <c r="H28" t="s">
         <v>146</v>
@@ -1748,28 +1748,28 @@
         <v>12</v>
       </c>
       <c r="C29">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="D29" t="s">
         <v>40</v>
       </c>
       <c r="E29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F29" t="s">
         <v>145</v>
       </c>
       <c r="G29" s="1">
-        <v>45047</v>
+        <v>45859</v>
       </c>
       <c r="H29" t="s">
         <v>146</v>
       </c>
       <c r="I29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J29" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1780,25 +1780,25 @@
         <v>12</v>
       </c>
       <c r="C30">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D30" t="s">
         <v>41</v>
       </c>
       <c r="E30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F30" t="s">
         <v>145</v>
       </c>
       <c r="G30" s="1">
-        <v>45859</v>
+        <v>45809</v>
       </c>
       <c r="H30" t="s">
         <v>146</v>
       </c>
       <c r="I30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J30" t="s">
         <v>161</v>
@@ -1812,19 +1812,19 @@
         <v>12</v>
       </c>
       <c r="C31">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F31" t="s">
         <v>145</v>
       </c>
       <c r="G31" s="1">
-        <v>45859</v>
+        <v>46017</v>
       </c>
       <c r="H31" t="s">
         <v>146</v>
@@ -1833,7 +1833,7 @@
         <v>149</v>
       </c>
       <c r="J31" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1844,28 +1844,28 @@
         <v>12</v>
       </c>
       <c r="C32">
-        <v>177</v>
+        <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E32" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F32" t="s">
         <v>145</v>
       </c>
       <c r="G32" s="1">
-        <v>45809</v>
+        <v>45313</v>
       </c>
       <c r="H32" t="s">
         <v>146</v>
       </c>
       <c r="I32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J32" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1876,28 +1876,28 @@
         <v>12</v>
       </c>
       <c r="C33">
-        <v>208</v>
+        <v>58</v>
       </c>
       <c r="D33" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F33" t="s">
         <v>145</v>
       </c>
       <c r="G33" s="1">
-        <v>46017</v>
+        <v>44858</v>
       </c>
       <c r="H33" t="s">
         <v>146</v>
       </c>
       <c r="I33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J33" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1908,19 +1908,19 @@
         <v>12</v>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>169</v>
       </c>
       <c r="D34" t="s">
         <v>44</v>
       </c>
       <c r="E34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F34" t="s">
         <v>145</v>
       </c>
       <c r="G34" s="1">
-        <v>45313</v>
+        <v>45600</v>
       </c>
       <c r="H34" t="s">
         <v>146</v>
@@ -1940,28 +1940,28 @@
         <v>12</v>
       </c>
       <c r="C35">
-        <v>58</v>
+        <v>207</v>
       </c>
       <c r="D35" t="s">
         <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F35" t="s">
         <v>145</v>
       </c>
       <c r="G35" s="1">
-        <v>44858</v>
+        <v>46197</v>
       </c>
       <c r="H35" t="s">
         <v>146</v>
       </c>
       <c r="I35" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J35" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1972,28 +1972,28 @@
         <v>12</v>
       </c>
       <c r="C36">
-        <v>169</v>
+        <v>217</v>
       </c>
       <c r="D36" t="s">
         <v>46</v>
       </c>
       <c r="E36" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F36" t="s">
         <v>145</v>
       </c>
       <c r="G36" s="1">
-        <v>45600</v>
+        <v>46113</v>
       </c>
       <c r="H36" t="s">
         <v>146</v>
       </c>
       <c r="I36" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2004,19 +2004,19 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D37" t="s">
         <v>47</v>
       </c>
       <c r="E37" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F37" t="s">
         <v>145</v>
       </c>
       <c r="G37" s="1">
-        <v>46197</v>
+        <v>46070</v>
       </c>
       <c r="H37" t="s">
         <v>146</v>
@@ -2025,7 +2025,7 @@
         <v>149</v>
       </c>
       <c r="J37" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2036,28 +2036,28 @@
         <v>12</v>
       </c>
       <c r="C38">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="D38" t="s">
         <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F38" t="s">
         <v>145</v>
       </c>
       <c r="G38" s="1">
-        <v>46113</v>
+        <v>46254</v>
       </c>
       <c r="H38" t="s">
         <v>146</v>
       </c>
       <c r="I38" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2068,19 +2068,19 @@
         <v>12</v>
       </c>
       <c r="C39">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="D39" t="s">
         <v>49</v>
       </c>
       <c r="E39" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F39" t="s">
         <v>145</v>
       </c>
       <c r="G39" s="1">
-        <v>46070</v>
+        <v>46181</v>
       </c>
       <c r="H39" t="s">
         <v>146</v>
@@ -2089,7 +2089,7 @@
         <v>149</v>
       </c>
       <c r="J39" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2100,19 +2100,19 @@
         <v>12</v>
       </c>
       <c r="C40">
-        <v>238</v>
+        <v>48</v>
       </c>
       <c r="D40" t="s">
         <v>50</v>
       </c>
       <c r="E40" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F40" t="s">
         <v>145</v>
       </c>
       <c r="G40" s="1">
-        <v>46254</v>
+        <v>44348</v>
       </c>
       <c r="H40" t="s">
         <v>146</v>
@@ -2121,7 +2121,7 @@
         <v>149</v>
       </c>
       <c r="J40" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2132,19 +2132,19 @@
         <v>12</v>
       </c>
       <c r="C41">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="D41" t="s">
         <v>51</v>
       </c>
       <c r="E41" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F41" t="s">
         <v>145</v>
       </c>
       <c r="G41" s="1">
-        <v>46181</v>
+        <v>46126</v>
       </c>
       <c r="H41" t="s">
         <v>146</v>
@@ -2153,7 +2153,7 @@
         <v>149</v>
       </c>
       <c r="J41" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2164,19 +2164,19 @@
         <v>12</v>
       </c>
       <c r="C42">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D42" t="s">
         <v>52</v>
       </c>
       <c r="E42" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F42" t="s">
         <v>145</v>
       </c>
       <c r="G42" s="1">
-        <v>44348</v>
+        <v>44802</v>
       </c>
       <c r="H42" t="s">
         <v>146</v>
@@ -2185,7 +2185,7 @@
         <v>149</v>
       </c>
       <c r="J42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2196,19 +2196,19 @@
         <v>12</v>
       </c>
       <c r="C43">
-        <v>122</v>
+        <v>234</v>
       </c>
       <c r="D43" t="s">
         <v>53</v>
       </c>
       <c r="E43" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F43" t="s">
         <v>145</v>
       </c>
       <c r="G43" s="1">
-        <v>46126</v>
+        <v>46237</v>
       </c>
       <c r="H43" t="s">
         <v>146</v>
@@ -2217,7 +2217,7 @@
         <v>149</v>
       </c>
       <c r="J43" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2228,19 +2228,19 @@
         <v>12</v>
       </c>
       <c r="C44">
-        <v>46</v>
+        <v>141</v>
       </c>
       <c r="D44" t="s">
         <v>54</v>
       </c>
       <c r="E44" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F44" t="s">
         <v>145</v>
       </c>
       <c r="G44" s="1">
-        <v>44802</v>
+        <v>45499</v>
       </c>
       <c r="H44" t="s">
         <v>146</v>
@@ -2249,7 +2249,7 @@
         <v>149</v>
       </c>
       <c r="J44" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2260,19 +2260,19 @@
         <v>12</v>
       </c>
       <c r="C45">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="D45" t="s">
         <v>55</v>
       </c>
       <c r="E45" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F45" t="s">
         <v>145</v>
       </c>
       <c r="G45" s="1">
-        <v>46237</v>
+        <v>45957</v>
       </c>
       <c r="H45" t="s">
         <v>146</v>
@@ -2281,7 +2281,7 @@
         <v>149</v>
       </c>
       <c r="J45" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2292,19 +2292,19 @@
         <v>12</v>
       </c>
       <c r="C46">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="D46" t="s">
         <v>56</v>
       </c>
       <c r="E46" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F46" t="s">
         <v>145</v>
       </c>
       <c r="G46" s="1">
-        <v>45499</v>
+        <v>45579</v>
       </c>
       <c r="H46" t="s">
         <v>146</v>
@@ -2313,7 +2313,7 @@
         <v>149</v>
       </c>
       <c r="J46" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2324,19 +2324,19 @@
         <v>12</v>
       </c>
       <c r="C47">
-        <v>200</v>
+        <v>147</v>
       </c>
       <c r="D47" t="s">
         <v>57</v>
       </c>
       <c r="E47" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F47" t="s">
         <v>145</v>
       </c>
       <c r="G47" s="1">
-        <v>45957</v>
+        <v>45509</v>
       </c>
       <c r="H47" t="s">
         <v>146</v>
@@ -2345,7 +2345,7 @@
         <v>149</v>
       </c>
       <c r="J47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2356,28 +2356,28 @@
         <v>12</v>
       </c>
       <c r="C48">
-        <v>15</v>
+        <v>235</v>
       </c>
       <c r="D48" t="s">
         <v>58</v>
       </c>
       <c r="E48" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F48" t="s">
         <v>145</v>
       </c>
       <c r="G48" s="1">
-        <v>43922</v>
+        <v>46244</v>
       </c>
       <c r="H48" t="s">
         <v>146</v>
       </c>
       <c r="I48" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J48" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -2388,28 +2388,28 @@
         <v>12</v>
       </c>
       <c r="C49">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="D49" t="s">
         <v>59</v>
       </c>
       <c r="E49" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F49" t="s">
         <v>145</v>
       </c>
       <c r="G49" s="1">
-        <v>45579</v>
+        <v>46181</v>
       </c>
       <c r="H49" t="s">
         <v>146</v>
       </c>
       <c r="I49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J49" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -2420,19 +2420,19 @@
         <v>12</v>
       </c>
       <c r="C50">
-        <v>147</v>
+        <v>218</v>
       </c>
       <c r="D50" t="s">
         <v>60</v>
       </c>
       <c r="E50" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F50" t="s">
         <v>145</v>
       </c>
       <c r="G50" s="1">
-        <v>45509</v>
+        <v>46127</v>
       </c>
       <c r="H50" t="s">
         <v>146</v>
@@ -2441,7 +2441,7 @@
         <v>149</v>
       </c>
       <c r="J50" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2452,19 +2452,19 @@
         <v>12</v>
       </c>
       <c r="C51">
-        <v>235</v>
+        <v>176</v>
       </c>
       <c r="D51" t="s">
         <v>61</v>
       </c>
       <c r="E51" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F51" t="s">
         <v>145</v>
       </c>
       <c r="G51" s="1">
-        <v>46244</v>
+        <v>45778</v>
       </c>
       <c r="H51" t="s">
         <v>146</v>
@@ -2473,30 +2473,30 @@
         <v>149</v>
       </c>
       <c r="J51" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
       </c>
       <c r="C52">
-        <v>1028</v>
+        <v>41</v>
       </c>
       <c r="D52" t="s">
         <v>62</v>
       </c>
       <c r="E52" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F52" t="s">
         <v>145</v>
       </c>
       <c r="G52" s="1">
-        <v>45239</v>
+        <v>44537</v>
       </c>
       <c r="H52" t="s">
         <v>146</v>
@@ -2505,7 +2505,7 @@
         <v>149</v>
       </c>
       <c r="J52" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -2516,51 +2516,51 @@
         <v>12</v>
       </c>
       <c r="C53">
-        <v>85</v>
+        <v>233</v>
       </c>
       <c r="D53" t="s">
         <v>63</v>
       </c>
       <c r="E53" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F53" t="s">
         <v>145</v>
       </c>
       <c r="G53" s="1">
-        <v>46181</v>
+        <v>46237</v>
       </c>
       <c r="H53" t="s">
         <v>146</v>
       </c>
       <c r="I53" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J53" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
       </c>
       <c r="C54">
-        <v>1043</v>
+        <v>166</v>
       </c>
       <c r="D54" t="s">
         <v>64</v>
       </c>
       <c r="E54" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F54" t="s">
         <v>145</v>
       </c>
       <c r="G54" s="1">
-        <v>45680</v>
+        <v>45586</v>
       </c>
       <c r="H54" t="s">
         <v>146</v>
@@ -2569,7 +2569,7 @@
         <v>149</v>
       </c>
       <c r="J54" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -2580,19 +2580,19 @@
         <v>12</v>
       </c>
       <c r="C55">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D55" t="s">
         <v>65</v>
       </c>
       <c r="E55" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F55" t="s">
         <v>145</v>
       </c>
       <c r="G55" s="1">
-        <v>46127</v>
+        <v>46048</v>
       </c>
       <c r="H55" t="s">
         <v>146</v>
@@ -2612,19 +2612,19 @@
         <v>12</v>
       </c>
       <c r="C56">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="E56" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F56" t="s">
         <v>145</v>
       </c>
       <c r="G56" s="1">
-        <v>45778</v>
+        <v>45243</v>
       </c>
       <c r="H56" t="s">
         <v>146</v>
@@ -2644,19 +2644,19 @@
         <v>12</v>
       </c>
       <c r="C57">
-        <v>41</v>
+        <v>240</v>
       </c>
       <c r="D57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E57" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F57" t="s">
         <v>145</v>
       </c>
       <c r="G57" s="1">
-        <v>44537</v>
+        <v>46265</v>
       </c>
       <c r="H57" t="s">
         <v>146</v>
@@ -2665,7 +2665,7 @@
         <v>149</v>
       </c>
       <c r="J57" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -2676,19 +2676,19 @@
         <v>12</v>
       </c>
       <c r="C58">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="D58" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="E58" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F58" t="s">
         <v>145</v>
       </c>
       <c r="G58" s="1">
-        <v>46237</v>
+        <v>46141</v>
       </c>
       <c r="H58" t="s">
         <v>146</v>
@@ -2697,39 +2697,39 @@
         <v>149</v>
       </c>
       <c r="J58" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
       </c>
       <c r="C59">
-        <v>1017</v>
+        <v>223</v>
       </c>
       <c r="D59" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E59" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F59" t="s">
         <v>145</v>
       </c>
       <c r="G59" s="1">
-        <v>45062</v>
+        <v>46163</v>
       </c>
       <c r="H59" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I59" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J59" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -2740,19 +2740,19 @@
         <v>12</v>
       </c>
       <c r="C60">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="D60" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E60" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F60" t="s">
         <v>145</v>
       </c>
       <c r="G60" s="1">
-        <v>45586</v>
+        <v>45432</v>
       </c>
       <c r="H60" t="s">
         <v>146</v>
@@ -2761,30 +2761,30 @@
         <v>149</v>
       </c>
       <c r="J60" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
       </c>
       <c r="C61">
-        <v>1041</v>
+        <v>65</v>
       </c>
       <c r="D61" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E61" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F61" t="s">
         <v>145</v>
       </c>
       <c r="G61" s="1">
-        <v>45689</v>
+        <v>44909</v>
       </c>
       <c r="H61" t="s">
         <v>146</v>
@@ -2804,19 +2804,19 @@
         <v>12</v>
       </c>
       <c r="C62">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D62" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E62" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F62" t="s">
         <v>145</v>
       </c>
       <c r="G62" s="1">
-        <v>46048</v>
+        <v>45978</v>
       </c>
       <c r="H62" t="s">
         <v>146</v>
@@ -2825,30 +2825,30 @@
         <v>149</v>
       </c>
       <c r="J62" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
       </c>
       <c r="C63">
-        <v>1027</v>
+        <v>199</v>
       </c>
       <c r="D63" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E63" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F63" t="s">
         <v>145</v>
       </c>
       <c r="G63" s="1">
-        <v>45176</v>
+        <v>45938</v>
       </c>
       <c r="H63" t="s">
         <v>146</v>
@@ -2857,7 +2857,7 @@
         <v>149</v>
       </c>
       <c r="J63" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -2868,10 +2868,10 @@
         <v>12</v>
       </c>
       <c r="C64">
-        <v>21</v>
+        <v>221</v>
       </c>
       <c r="D64" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E64" t="s">
         <v>136</v>
@@ -2880,7 +2880,7 @@
         <v>145</v>
       </c>
       <c r="G64" s="1">
-        <v>45243</v>
+        <v>46146</v>
       </c>
       <c r="H64" t="s">
         <v>146</v>
@@ -2889,7 +2889,7 @@
         <v>149</v>
       </c>
       <c r="J64" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -2900,19 +2900,19 @@
         <v>12</v>
       </c>
       <c r="C65">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D65" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="E65" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F65" t="s">
         <v>145</v>
       </c>
       <c r="G65" s="1">
-        <v>46141</v>
+        <v>46076</v>
       </c>
       <c r="H65" t="s">
         <v>146</v>
@@ -2926,34 +2926,34 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
       </c>
       <c r="C66">
-        <v>1013</v>
+        <v>127</v>
       </c>
       <c r="D66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E66" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F66" t="s">
         <v>145</v>
       </c>
       <c r="G66" s="1">
-        <v>44929</v>
+        <v>45444</v>
       </c>
       <c r="H66" t="s">
         <v>146</v>
       </c>
       <c r="I66" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J66" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -2964,19 +2964,19 @@
         <v>12</v>
       </c>
       <c r="C67">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D67" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F67" t="s">
         <v>145</v>
       </c>
       <c r="G67" s="1">
-        <v>46163</v>
+        <v>46076</v>
       </c>
       <c r="H67" t="s">
         <v>146</v>
@@ -2985,7 +2985,7 @@
         <v>149</v>
       </c>
       <c r="J67" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -2996,10 +2996,10 @@
         <v>12</v>
       </c>
       <c r="C68">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="D68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E68" t="s">
         <v>137</v>
@@ -3008,16 +3008,16 @@
         <v>145</v>
       </c>
       <c r="G68" s="1">
-        <v>45432</v>
+        <v>45894</v>
       </c>
       <c r="H68" t="s">
         <v>146</v>
       </c>
       <c r="I68" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -3028,10 +3028,10 @@
         <v>12</v>
       </c>
       <c r="C69">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E69" t="s">
         <v>138</v>
@@ -3040,7 +3040,7 @@
         <v>145</v>
       </c>
       <c r="G69" s="1">
-        <v>44909</v>
+        <v>44287</v>
       </c>
       <c r="H69" t="s">
         <v>146</v>
@@ -3049,7 +3049,7 @@
         <v>149</v>
       </c>
       <c r="J69" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -3060,13 +3060,13 @@
         <v>12</v>
       </c>
       <c r="C70">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D70" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E70" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F70" t="s">
         <v>145</v>
@@ -3081,7 +3081,7 @@
         <v>149</v>
       </c>
       <c r="J70" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -3092,19 +3092,19 @@
         <v>12</v>
       </c>
       <c r="C71">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="D71" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E71" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F71" t="s">
         <v>145</v>
       </c>
       <c r="G71" s="1">
-        <v>45938</v>
+        <v>44683</v>
       </c>
       <c r="H71" t="s">
         <v>146</v>
@@ -3113,7 +3113,7 @@
         <v>149</v>
       </c>
       <c r="J71" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3124,28 +3124,28 @@
         <v>12</v>
       </c>
       <c r="C72">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="D72" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="E72" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F72" t="s">
         <v>145</v>
       </c>
       <c r="G72" s="1">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="H72" t="s">
         <v>146</v>
       </c>
       <c r="I72" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J72" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -3156,19 +3156,19 @@
         <v>12</v>
       </c>
       <c r="C73">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="D73" t="s">
         <v>80</v>
       </c>
       <c r="E73" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F73" t="s">
         <v>145</v>
       </c>
       <c r="G73" s="1">
-        <v>46076</v>
+        <v>45873</v>
       </c>
       <c r="H73" t="s">
         <v>146</v>
@@ -3177,7 +3177,7 @@
         <v>149</v>
       </c>
       <c r="J73" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3188,7 +3188,7 @@
         <v>12</v>
       </c>
       <c r="C74">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="D74" t="s">
         <v>81</v>
@@ -3200,27 +3200,27 @@
         <v>145</v>
       </c>
       <c r="G74" s="1">
-        <v>45444</v>
+        <v>45121</v>
       </c>
       <c r="H74" t="s">
         <v>146</v>
       </c>
       <c r="I74" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J74" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
       </c>
       <c r="C75">
-        <v>1008</v>
+        <v>198</v>
       </c>
       <c r="D75" t="s">
         <v>82</v>
@@ -3232,7 +3232,7 @@
         <v>145</v>
       </c>
       <c r="G75" s="1">
-        <v>46007</v>
+        <v>45936</v>
       </c>
       <c r="H75" t="s">
         <v>146</v>
@@ -3241,7 +3241,7 @@
         <v>149</v>
       </c>
       <c r="J75" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3252,19 +3252,19 @@
         <v>12</v>
       </c>
       <c r="C76">
-        <v>214</v>
+        <v>133</v>
       </c>
       <c r="D76" t="s">
         <v>83</v>
       </c>
       <c r="E76" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F76" t="s">
         <v>145</v>
       </c>
       <c r="G76" s="1">
-        <v>46076</v>
+        <v>45957</v>
       </c>
       <c r="H76" t="s">
         <v>146</v>
@@ -3273,7 +3273,7 @@
         <v>149</v>
       </c>
       <c r="J76" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3284,51 +3284,51 @@
         <v>12</v>
       </c>
       <c r="C77">
-        <v>189</v>
+        <v>3</v>
       </c>
       <c r="D77" t="s">
         <v>84</v>
       </c>
       <c r="E77" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F77" t="s">
         <v>145</v>
       </c>
       <c r="G77" s="1">
-        <v>45894</v>
+        <v>44348</v>
       </c>
       <c r="H77" t="s">
         <v>146</v>
       </c>
       <c r="I77" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J77" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B78" t="s">
         <v>12</v>
       </c>
       <c r="C78">
-        <v>9</v>
+        <v>1012</v>
       </c>
       <c r="D78" t="s">
         <v>85</v>
       </c>
       <c r="E78" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="F78" t="s">
         <v>145</v>
       </c>
       <c r="G78" s="1">
-        <v>44287</v>
+        <v>44929</v>
       </c>
       <c r="H78" t="s">
         <v>146</v>
@@ -3337,30 +3337,30 @@
         <v>149</v>
       </c>
       <c r="J78" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
       </c>
       <c r="C79">
-        <v>204</v>
+        <v>1040</v>
       </c>
       <c r="D79" t="s">
         <v>86</v>
       </c>
       <c r="E79" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="F79" t="s">
         <v>145</v>
       </c>
       <c r="G79" s="1">
-        <v>45978</v>
+        <v>45684</v>
       </c>
       <c r="H79" t="s">
         <v>146</v>
@@ -3369,68 +3369,68 @@
         <v>149</v>
       </c>
       <c r="J79" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B80" t="s">
         <v>12</v>
       </c>
       <c r="C80">
-        <v>22</v>
+        <v>1044</v>
       </c>
       <c r="D80" t="s">
         <v>87</v>
       </c>
       <c r="E80" t="s">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="F80" t="s">
         <v>145</v>
       </c>
       <c r="G80" s="1">
-        <v>44683</v>
+        <v>45689</v>
       </c>
       <c r="H80" t="s">
         <v>146</v>
       </c>
       <c r="I80" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J80" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B81" t="s">
         <v>12</v>
       </c>
       <c r="C81">
-        <v>228</v>
+        <v>1028</v>
       </c>
       <c r="D81" t="s">
         <v>88</v>
       </c>
       <c r="E81" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="F81" t="s">
         <v>145</v>
       </c>
       <c r="G81" s="1">
-        <v>46153</v>
+        <v>45239</v>
       </c>
       <c r="H81" t="s">
         <v>146</v>
       </c>
       <c r="I81" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J81" t="s">
         <v>163</v>
@@ -3438,25 +3438,25 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
       </c>
       <c r="C82">
-        <v>187</v>
+        <v>1043</v>
       </c>
       <c r="D82" t="s">
         <v>89</v>
       </c>
       <c r="E82" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="F82" t="s">
         <v>145</v>
       </c>
       <c r="G82" s="1">
-        <v>45873</v>
+        <v>45680</v>
       </c>
       <c r="H82" t="s">
         <v>146</v>
@@ -3465,18 +3465,18 @@
         <v>149</v>
       </c>
       <c r="J82" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B83" t="s">
         <v>12</v>
       </c>
       <c r="C83">
-        <v>84</v>
+        <v>1017</v>
       </c>
       <c r="D83" t="s">
         <v>90</v>
@@ -3488,39 +3488,39 @@
         <v>145</v>
       </c>
       <c r="G83" s="1">
-        <v>45121</v>
+        <v>45062</v>
       </c>
       <c r="H83" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I83" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J83" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B84" t="s">
         <v>12</v>
       </c>
       <c r="C84">
-        <v>198</v>
+        <v>1041</v>
       </c>
       <c r="D84" t="s">
         <v>91</v>
       </c>
       <c r="E84" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F84" t="s">
         <v>145</v>
       </c>
       <c r="G84" s="1">
-        <v>45936</v>
+        <v>45689</v>
       </c>
       <c r="H84" t="s">
         <v>146</v>
@@ -3529,30 +3529,30 @@
         <v>149</v>
       </c>
       <c r="J84" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B85" t="s">
         <v>12</v>
       </c>
       <c r="C85">
-        <v>133</v>
+        <v>1027</v>
       </c>
       <c r="D85" t="s">
         <v>92</v>
       </c>
       <c r="E85" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F85" t="s">
         <v>145</v>
       </c>
       <c r="G85" s="1">
-        <v>45957</v>
+        <v>45176</v>
       </c>
       <c r="H85" t="s">
         <v>146</v>
@@ -3561,30 +3561,30 @@
         <v>149</v>
       </c>
       <c r="J85" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
       </c>
       <c r="C86">
-        <v>3</v>
+        <v>1013</v>
       </c>
       <c r="D86" t="s">
         <v>93</v>
       </c>
       <c r="E86" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="F86" t="s">
         <v>145</v>
       </c>
       <c r="G86" s="1">
-        <v>44348</v>
+        <v>44929</v>
       </c>
       <c r="H86" t="s">
         <v>146</v>
@@ -3593,7 +3593,39 @@
         <v>149</v>
       </c>
       <c r="J86" t="s">
-        <v>153</v>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87">
+        <v>1008</v>
+      </c>
+      <c r="D87" t="s">
+        <v>94</v>
+      </c>
+      <c r="E87" t="s">
+        <v>136</v>
+      </c>
+      <c r="F87" t="s">
+        <v>145</v>
+      </c>
+      <c r="G87" s="1">
+        <v>46007</v>
+      </c>
+      <c r="H87" t="s">
+        <v>146</v>
+      </c>
+      <c r="I87" t="s">
+        <v>149</v>
+      </c>
+      <c r="J87" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
